--- a/research/traditional_assets/database/data/kuwait/kuwait_food_processing.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_food_processing.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07826342015223542</v>
+        <v>0.07818427502200705</v>
       </c>
       <c r="C2">
-        <v>1233.536261462596</v>
+        <v>1224.432444786622</v>
       </c>
       <c r="D2">
-        <v>1171.136261462596</v>
+        <v>1173.998444786621</v>
       </c>
       <c r="E2">
-        <v>-287.7</v>
+        <v>-275.734</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.966</v>
       </c>
       <c r="G2">
         <v>62.4</v>
@@ -1457,28 +1457,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6018897999999999</v>
       </c>
       <c r="N2">
-        <v>93.52499999999999</v>
+        <v>92.9231102</v>
       </c>
       <c r="O2">
-        <v>14.02875</v>
+        <v>13.93846653</v>
       </c>
       <c r="P2">
-        <v>79.49624999999999</v>
+        <v>78.98464367</v>
       </c>
       <c r="Q2">
-        <v>102.59625</v>
+        <v>102.08464367</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07826342015223542</v>
+        <v>0.07854214648687581</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.6211064198843799</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>155.3855871955298</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07818427502200705</v>
+        <v>0.0781051298917787</v>
       </c>
       <c r="C3">
-        <v>1224.432444786622</v>
+        <v>1215.342652376926</v>
       </c>
       <c r="D3">
-        <v>1173.998444786621</v>
+        <v>1176.874652376926</v>
       </c>
       <c r="E3">
-        <v>-275.734</v>
+        <v>-263.768</v>
       </c>
       <c r="F3">
-        <v>11.966</v>
+        <v>23.932</v>
       </c>
       <c r="G3">
         <v>62.4</v>
@@ -1539,28 +1539,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M3">
-        <v>0.6018897999999999</v>
+        <v>1.2037796</v>
       </c>
       <c r="N3">
-        <v>92.9231102</v>
+        <v>92.32122039999999</v>
       </c>
       <c r="O3">
-        <v>13.93846653</v>
+        <v>13.84818306</v>
       </c>
       <c r="P3">
-        <v>78.98464367</v>
+        <v>78.47303733999999</v>
       </c>
       <c r="Q3">
-        <v>102.08464367</v>
+        <v>101.57303734</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07854214648687581</v>
+        <v>0.0788265611140599</v>
       </c>
       <c r="T3">
-        <v>0.6211064198843799</v>
+        <v>0.6265016602643553</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>155.3855871955298</v>
+        <v>77.6927935977649</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0781051298917787</v>
+        <v>0.07802598476155034</v>
       </c>
       <c r="C4">
-        <v>1215.342652376926</v>
+        <v>1206.266987561841</v>
       </c>
       <c r="D4">
-        <v>1176.874652376926</v>
+        <v>1179.76498756184</v>
       </c>
       <c r="E4">
-        <v>-263.768</v>
+        <v>-251.802</v>
       </c>
       <c r="F4">
-        <v>23.932</v>
+        <v>35.898</v>
       </c>
       <c r="G4">
         <v>62.4</v>
@@ -1621,28 +1621,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M4">
-        <v>1.2037796</v>
+        <v>1.8056694</v>
       </c>
       <c r="N4">
-        <v>92.32122039999999</v>
+        <v>91.71933059999999</v>
       </c>
       <c r="O4">
-        <v>13.84818306</v>
+        <v>13.75789959</v>
       </c>
       <c r="P4">
-        <v>78.47303733999999</v>
+        <v>77.96143101</v>
       </c>
       <c r="Q4">
-        <v>101.57303734</v>
+        <v>101.06143101</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0788265611140599</v>
+        <v>0.07911683996036119</v>
       </c>
       <c r="T4">
-        <v>0.6265016602643553</v>
+        <v>0.6320081427140207</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.6927935977649</v>
+        <v>51.79519573184327</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07802598476155034</v>
+        <v>0.07794683963132198</v>
       </c>
       <c r="C5">
-        <v>1206.266987561841</v>
+        <v>1197.205554687265</v>
       </c>
       <c r="D5">
-        <v>1179.76498756184</v>
+        <v>1182.669554687265</v>
       </c>
       <c r="E5">
-        <v>-251.802</v>
+        <v>-239.836</v>
       </c>
       <c r="F5">
-        <v>35.898</v>
+        <v>47.864</v>
       </c>
       <c r="G5">
         <v>62.4</v>
@@ -1703,28 +1703,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M5">
-        <v>1.8056694</v>
+        <v>2.4075592</v>
       </c>
       <c r="N5">
-        <v>91.71933059999999</v>
+        <v>91.1174408</v>
       </c>
       <c r="O5">
-        <v>13.75789959</v>
+        <v>13.66761612</v>
       </c>
       <c r="P5">
-        <v>77.96143101</v>
+        <v>77.44982467999999</v>
       </c>
       <c r="Q5">
-        <v>101.06143101</v>
+        <v>100.54982468</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07911683996036119</v>
+        <v>0.07941316628262708</v>
       </c>
       <c r="T5">
-        <v>0.6320081427140207</v>
+        <v>0.6376293435480543</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.79519573184327</v>
+        <v>38.84639679888246</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07794683963132198</v>
+        <v>0.07786769450109363</v>
       </c>
       <c r="C6">
-        <v>1197.205554687265</v>
+        <v>1188.158459129231</v>
       </c>
       <c r="D6">
-        <v>1182.669554687265</v>
+        <v>1185.588459129231</v>
       </c>
       <c r="E6">
-        <v>-239.836</v>
+        <v>-227.87</v>
       </c>
       <c r="F6">
-        <v>47.864</v>
+        <v>59.83</v>
       </c>
       <c r="G6">
         <v>62.4</v>
@@ -1785,28 +1785,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M6">
-        <v>2.4075592</v>
+        <v>3.009449</v>
       </c>
       <c r="N6">
-        <v>91.1174408</v>
+        <v>90.51555099999999</v>
       </c>
       <c r="O6">
-        <v>13.66761612</v>
+        <v>13.57733265</v>
       </c>
       <c r="P6">
-        <v>77.44982467999999</v>
+        <v>76.93821834999999</v>
       </c>
       <c r="Q6">
-        <v>100.54982468</v>
+        <v>100.03821835</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07941316628262708</v>
+        <v>0.07971573105378278</v>
       </c>
       <c r="T6">
-        <v>0.6376293435480543</v>
+        <v>0.643368885452278</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.84639679888246</v>
+        <v>31.07711743910596</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07786769450109363</v>
+        <v>0.07778854937086528</v>
       </c>
       <c r="C7">
-        <v>1188.158459129231</v>
+        <v>1179.125807306641</v>
       </c>
       <c r="D7">
-        <v>1185.588459129231</v>
+        <v>1188.521807306641</v>
       </c>
       <c r="E7">
-        <v>-227.87</v>
+        <v>-215.904</v>
       </c>
       <c r="F7">
-        <v>59.83</v>
+        <v>71.79600000000001</v>
       </c>
       <c r="G7">
         <v>62.4</v>
@@ -1867,28 +1867,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M7">
-        <v>3.009449</v>
+        <v>3.6113388</v>
       </c>
       <c r="N7">
-        <v>90.51555099999999</v>
+        <v>89.91366119999999</v>
       </c>
       <c r="O7">
-        <v>13.57733265</v>
+        <v>13.48704918</v>
       </c>
       <c r="P7">
-        <v>76.93821834999999</v>
+        <v>76.42661201999999</v>
       </c>
       <c r="Q7">
-        <v>100.03821835</v>
+        <v>99.52661201999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07971573105378278</v>
+        <v>0.08002473337326094</v>
       </c>
       <c r="T7">
-        <v>0.643368885452278</v>
+        <v>0.6492305452693575</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.07711743910596</v>
+        <v>25.89759786592163</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07778854937086527</v>
+        <v>0.07770940424063695</v>
       </c>
       <c r="C8">
-        <v>1179.125807306641</v>
+        <v>1170.107706694204</v>
       </c>
       <c r="D8">
-        <v>1188.521807306641</v>
+        <v>1191.469706694204</v>
       </c>
       <c r="E8">
-        <v>-215.904</v>
+        <v>-203.938</v>
       </c>
       <c r="F8">
-        <v>71.79599999999999</v>
+        <v>83.76199999999999</v>
       </c>
       <c r="G8">
         <v>62.4</v>
@@ -1949,28 +1949,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M8">
-        <v>3.6113388</v>
+        <v>4.213228599999999</v>
       </c>
       <c r="N8">
-        <v>89.91366119999999</v>
+        <v>89.3117714</v>
       </c>
       <c r="O8">
-        <v>13.48704918</v>
+        <v>13.39676571</v>
       </c>
       <c r="P8">
-        <v>76.42661201999999</v>
+        <v>75.91500569</v>
       </c>
       <c r="Q8">
-        <v>99.52661201999999</v>
+        <v>99.01500569</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08002473337326094</v>
+        <v>0.08034038090391069</v>
       </c>
       <c r="T8">
-        <v>0.6492305452693575</v>
+        <v>0.6552182622868045</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.89759786592164</v>
+        <v>22.19794102793283</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07770940424063694</v>
+        <v>0.07763025911040859</v>
       </c>
       <c r="C9">
-        <v>1170.107706694205</v>
+        <v>1161.104265835566</v>
       </c>
       <c r="D9">
-        <v>1191.469706694204</v>
+        <v>1194.432265835566</v>
       </c>
       <c r="E9">
-        <v>-203.938</v>
+        <v>-191.972</v>
       </c>
       <c r="F9">
-        <v>83.762</v>
+        <v>95.72799999999999</v>
       </c>
       <c r="G9">
         <v>62.4</v>
@@ -2031,28 +2031,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M9">
-        <v>4.2132286</v>
+        <v>4.815118399999999</v>
       </c>
       <c r="N9">
-        <v>89.3117714</v>
+        <v>88.70988159999999</v>
       </c>
       <c r="O9">
-        <v>13.39676571</v>
+        <v>13.30648224</v>
       </c>
       <c r="P9">
-        <v>75.91500569</v>
+        <v>75.40339935999999</v>
       </c>
       <c r="Q9">
-        <v>99.01500569</v>
+        <v>98.50339935999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08034038090391069</v>
+        <v>0.08066289033740064</v>
       </c>
       <c r="T9">
-        <v>0.6552182622868045</v>
+        <v>0.6613361470655001</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.19794102793283</v>
+        <v>19.42319839944123</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07763025911040859</v>
+        <v>0.07755111398018023</v>
       </c>
       <c r="C10">
-        <v>1161.104265835566</v>
+        <v>1152.115594356623</v>
       </c>
       <c r="D10">
-        <v>1194.432265835566</v>
+        <v>1197.409594356622</v>
       </c>
       <c r="E10">
-        <v>-191.972</v>
+        <v>-180.006</v>
       </c>
       <c r="F10">
-        <v>95.72799999999999</v>
+        <v>107.694</v>
       </c>
       <c r="G10">
         <v>62.4</v>
@@ -2113,28 +2113,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M10">
-        <v>4.815118399999999</v>
+        <v>5.417008199999999</v>
       </c>
       <c r="N10">
-        <v>88.70988159999999</v>
+        <v>88.10799179999999</v>
       </c>
       <c r="O10">
-        <v>13.30648224</v>
+        <v>13.21619877</v>
       </c>
       <c r="P10">
-        <v>75.40339935999999</v>
+        <v>74.89179303</v>
       </c>
       <c r="Q10">
-        <v>98.50339935999999</v>
+        <v>97.99179303</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08066289033740064</v>
+        <v>0.08099248789030794</v>
       </c>
       <c r="T10">
-        <v>0.6613361470655001</v>
+        <v>0.6675884908503209</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.42319839944123</v>
+        <v>17.26506524394776</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07755111398018023</v>
+        <v>0.07747196884995189</v>
       </c>
       <c r="C11">
-        <v>1152.115594356623</v>
+        <v>1143.141802979048</v>
       </c>
       <c r="D11">
-        <v>1197.409594356622</v>
+        <v>1200.401802979048</v>
       </c>
       <c r="E11">
-        <v>-180.006</v>
+        <v>-168.04</v>
       </c>
       <c r="F11">
-        <v>107.694</v>
+        <v>119.66</v>
       </c>
       <c r="G11">
         <v>62.4</v>
@@ -2195,28 +2195,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M11">
-        <v>5.417008199999999</v>
+        <v>6.018897999999999</v>
       </c>
       <c r="N11">
-        <v>88.10799179999999</v>
+        <v>87.506102</v>
       </c>
       <c r="O11">
-        <v>13.21619877</v>
+        <v>13.1259153</v>
       </c>
       <c r="P11">
-        <v>74.89179303</v>
+        <v>74.3801867</v>
       </c>
       <c r="Q11">
-        <v>97.99179303</v>
+        <v>97.48018669999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08099248789030794</v>
+        <v>0.08132940983327987</v>
       </c>
       <c r="T11">
-        <v>0.6675884908503209</v>
+        <v>0.6739797756081379</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.26506524394776</v>
+        <v>15.53855871955298</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07747196884995189</v>
+        <v>0.07739282371972353</v>
       </c>
       <c r="C12">
-        <v>1143.141802979048</v>
+        <v>1134.183003534022</v>
       </c>
       <c r="D12">
-        <v>1200.401802979048</v>
+        <v>1203.409003534022</v>
       </c>
       <c r="E12">
-        <v>-168.04</v>
+        <v>-156.074</v>
       </c>
       <c r="F12">
-        <v>119.66</v>
+        <v>131.626</v>
       </c>
       <c r="G12">
         <v>62.4</v>
@@ -2277,28 +2277,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M12">
-        <v>6.018897999999999</v>
+        <v>6.6207878</v>
       </c>
       <c r="N12">
-        <v>87.506102</v>
+        <v>86.90421219999999</v>
       </c>
       <c r="O12">
-        <v>13.1259153</v>
+        <v>13.03563183</v>
       </c>
       <c r="P12">
-        <v>74.3801867</v>
+        <v>73.86858036999999</v>
       </c>
       <c r="Q12">
-        <v>97.48018669999999</v>
+        <v>96.96858036999998</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08132940983327987</v>
+        <v>0.08167390305586913</v>
       </c>
       <c r="T12">
-        <v>0.6739797756081379</v>
+        <v>0.680514684742535</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.53855871955298</v>
+        <v>14.12596247232089</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07739282371972353</v>
+        <v>0.07731367858949517</v>
       </c>
       <c r="C13">
-        <v>1134.183003534022</v>
+        <v>1125.239308976155</v>
       </c>
       <c r="D13">
-        <v>1203.409003534022</v>
+        <v>1206.431308976155</v>
       </c>
       <c r="E13">
-        <v>-156.074</v>
+        <v>-144.108</v>
       </c>
       <c r="F13">
-        <v>131.626</v>
+        <v>143.592</v>
       </c>
       <c r="G13">
         <v>62.4</v>
@@ -2359,28 +2359,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M13">
-        <v>6.6207878</v>
+        <v>7.222677599999999</v>
       </c>
       <c r="N13">
-        <v>86.90421219999999</v>
+        <v>86.30232239999999</v>
       </c>
       <c r="O13">
-        <v>13.03563183</v>
+        <v>12.94534836</v>
       </c>
       <c r="P13">
-        <v>73.86858036999999</v>
+        <v>73.35697404</v>
       </c>
       <c r="Q13">
-        <v>96.96858036999998</v>
+        <v>96.45697403999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08167390305586913</v>
+        <v>0.08202622566988088</v>
       </c>
       <c r="T13">
-        <v>0.680514684742535</v>
+        <v>0.6871981145390774</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.12596247232089</v>
+        <v>12.94879893296082</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07731367858949517</v>
+        <v>0.07740028345926682</v>
       </c>
       <c r="C14">
-        <v>1125.239308976155</v>
+        <v>1109.966920078189</v>
       </c>
       <c r="D14">
-        <v>1206.431308976155</v>
+        <v>1203.124920078189</v>
       </c>
       <c r="E14">
-        <v>-144.108</v>
+        <v>-132.142</v>
       </c>
       <c r="F14">
-        <v>143.592</v>
+        <v>155.558</v>
       </c>
       <c r="G14">
         <v>62.4</v>
@@ -2441,45 +2441,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M14">
-        <v>7.222677599999999</v>
+        <v>8.0579044</v>
       </c>
       <c r="N14">
-        <v>86.30232239999999</v>
+        <v>85.46709559999999</v>
       </c>
       <c r="O14">
-        <v>12.94534836</v>
+        <v>12.82006434</v>
       </c>
       <c r="P14">
-        <v>73.35697404</v>
+        <v>72.64703125999999</v>
       </c>
       <c r="Q14">
-        <v>96.45697403999999</v>
+        <v>95.74703125999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08202622566988088</v>
+        <v>0.08238664765432968</v>
       </c>
       <c r="T14">
-        <v>0.6871981145390774</v>
+        <v>0.6940351863999081</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>12.94879893296082</v>
+        <v>11.60661573497943</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07740028345926682</v>
+        <v>0.07733388832903847</v>
       </c>
       <c r="C15">
-        <v>1109.966920078189</v>
+        <v>1100.53411975582</v>
       </c>
       <c r="D15">
-        <v>1203.124920078189</v>
+        <v>1205.65811975582</v>
       </c>
       <c r="E15">
-        <v>-132.142</v>
+        <v>-120.176</v>
       </c>
       <c r="F15">
-        <v>155.558</v>
+        <v>167.524</v>
       </c>
       <c r="G15">
         <v>62.4</v>
@@ -2523,28 +2523,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M15">
-        <v>8.0579044</v>
+        <v>8.6777432</v>
       </c>
       <c r="N15">
-        <v>85.46709559999999</v>
+        <v>84.8472568</v>
       </c>
       <c r="O15">
-        <v>12.82006434</v>
+        <v>12.72708852</v>
       </c>
       <c r="P15">
-        <v>72.64703125999999</v>
+        <v>72.12016828</v>
       </c>
       <c r="Q15">
-        <v>95.74703125999999</v>
+        <v>95.22016828</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08238664765432968</v>
+        <v>0.08275545154539357</v>
       </c>
       <c r="T15">
-        <v>0.6940351863999081</v>
+        <v>0.7010312599319209</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.60661573497943</v>
+        <v>10.77757175390947</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07733388832903847</v>
+        <v>0.07726749319881011</v>
       </c>
       <c r="C16">
-        <v>1100.53411975582</v>
+        <v>1091.112009329937</v>
       </c>
       <c r="D16">
-        <v>1205.65811975582</v>
+        <v>1208.202009329937</v>
       </c>
       <c r="E16">
-        <v>-120.176</v>
+        <v>-108.21</v>
       </c>
       <c r="F16">
-        <v>167.524</v>
+        <v>179.49</v>
       </c>
       <c r="G16">
         <v>62.4</v>
@@ -2605,28 +2605,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M16">
-        <v>8.6777432</v>
+        <v>9.297582</v>
       </c>
       <c r="N16">
-        <v>84.8472568</v>
+        <v>84.22741799999999</v>
       </c>
       <c r="O16">
-        <v>12.72708852</v>
+        <v>12.6341127</v>
       </c>
       <c r="P16">
-        <v>72.12016828</v>
+        <v>71.59330529999998</v>
       </c>
       <c r="Q16">
-        <v>95.22016828</v>
+        <v>94.69330529999998</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08275545154539357</v>
+        <v>0.08313293317507073</v>
       </c>
       <c r="T16">
-        <v>0.7010312599319209</v>
+        <v>0.7081919469588047</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.77757175390947</v>
+        <v>10.05906697031551</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07726749319881011</v>
+        <v>0.07743229806858178</v>
       </c>
       <c r="C17">
-        <v>1091.112009329937</v>
+        <v>1072.85125406512</v>
       </c>
       <c r="D17">
-        <v>1208.202009329937</v>
+        <v>1201.907254065119</v>
       </c>
       <c r="E17">
-        <v>-108.21</v>
+        <v>-96.244</v>
       </c>
       <c r="F17">
-        <v>179.49</v>
+        <v>191.456</v>
       </c>
       <c r="G17">
         <v>62.4</v>
@@ -2687,45 +2687,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M17">
-        <v>9.297581999999998</v>
+        <v>10.242896</v>
       </c>
       <c r="N17">
-        <v>84.227418</v>
+        <v>83.28210399999999</v>
       </c>
       <c r="O17">
-        <v>12.6341127</v>
+        <v>12.4923156</v>
       </c>
       <c r="P17">
-        <v>71.5933053</v>
+        <v>70.78978839999999</v>
       </c>
       <c r="Q17">
-        <v>94.69330529999999</v>
+        <v>93.88978839999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08313293317507073</v>
+        <v>0.08351940246259734</v>
       </c>
       <c r="T17">
-        <v>0.7081919469588047</v>
+        <v>0.7155231265339478</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.05906697031551</v>
+        <v>9.130718499924239</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07743229806858178</v>
+        <v>0.07738035293835339</v>
       </c>
       <c r="C18">
-        <v>1072.85125406512</v>
+        <v>1062.862218317442</v>
       </c>
       <c r="D18">
-        <v>1201.907254065119</v>
+        <v>1203.884218317442</v>
       </c>
       <c r="E18">
-        <v>-96.244</v>
+        <v>-84.27799999999999</v>
       </c>
       <c r="F18">
-        <v>191.456</v>
+        <v>203.422</v>
       </c>
       <c r="G18">
         <v>62.4</v>
@@ -2769,28 +2769,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M18">
-        <v>10.242896</v>
+        <v>10.883077</v>
       </c>
       <c r="N18">
-        <v>83.28210399999999</v>
+        <v>82.64192299999999</v>
       </c>
       <c r="O18">
-        <v>12.4923156</v>
+        <v>12.39628845</v>
       </c>
       <c r="P18">
-        <v>70.78978839999999</v>
+        <v>70.24563454999999</v>
       </c>
       <c r="Q18">
-        <v>93.88978839999999</v>
+        <v>93.34563454999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08351940246259734</v>
+        <v>0.0839151842630764</v>
       </c>
       <c r="T18">
-        <v>0.7155231265339478</v>
+        <v>0.7230309610386121</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.130718499924239</v>
+        <v>8.593617411693401</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07738035293835339</v>
+        <v>0.07732840780812504</v>
       </c>
       <c r="C19">
-        <v>1062.862218317442</v>
+        <v>1052.879696927619</v>
       </c>
       <c r="D19">
-        <v>1203.884218317442</v>
+        <v>1205.867696927619</v>
       </c>
       <c r="E19">
-        <v>-84.27799999999999</v>
+        <v>-72.31199999999998</v>
       </c>
       <c r="F19">
-        <v>203.422</v>
+        <v>215.388</v>
       </c>
       <c r="G19">
         <v>62.4</v>
@@ -2851,28 +2851,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M19">
-        <v>10.883077</v>
+        <v>11.523258</v>
       </c>
       <c r="N19">
-        <v>82.64192299999999</v>
+        <v>82.00174199999999</v>
       </c>
       <c r="O19">
-        <v>12.39628845</v>
+        <v>12.3002613</v>
       </c>
       <c r="P19">
-        <v>70.24563454999999</v>
+        <v>69.70148069999999</v>
       </c>
       <c r="Q19">
-        <v>93.34563454999999</v>
+        <v>92.80148069999998</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0839151842630764</v>
+        <v>0.08432061927820128</v>
       </c>
       <c r="T19">
-        <v>0.7230309610386121</v>
+        <v>0.7307219134580244</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.593617411693401</v>
+        <v>8.11619422215488</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07732840780812505</v>
+        <v>0.0772764626778967</v>
       </c>
       <c r="C20">
-        <v>1052.879696927618</v>
+        <v>1042.90372214729</v>
       </c>
       <c r="D20">
-        <v>1205.867696927618</v>
+        <v>1207.85772214729</v>
       </c>
       <c r="E20">
-        <v>-72.31200000000001</v>
+        <v>-60.346</v>
       </c>
       <c r="F20">
-        <v>215.388</v>
+        <v>227.354</v>
       </c>
       <c r="G20">
         <v>62.4</v>
@@ -2933,28 +2933,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M20">
-        <v>11.523258</v>
+        <v>12.163439</v>
       </c>
       <c r="N20">
-        <v>82.00174199999999</v>
+        <v>81.36156099999999</v>
       </c>
       <c r="O20">
-        <v>12.3002613</v>
+        <v>12.20423415</v>
       </c>
       <c r="P20">
-        <v>69.70148069999999</v>
+        <v>69.15732684999999</v>
       </c>
       <c r="Q20">
-        <v>92.80148069999998</v>
+        <v>92.25732684999998</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08432061927820128</v>
+        <v>0.08473606503444037</v>
       </c>
       <c r="T20">
-        <v>0.7307219134580244</v>
+        <v>0.7386027659371753</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.116194222154881</v>
+        <v>7.68902610519936</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0772764626778967</v>
+        <v>0.07736051754766836</v>
       </c>
       <c r="C21">
-        <v>1042.90372214729</v>
+        <v>1027.720844496775</v>
       </c>
       <c r="D21">
-        <v>1207.85772214729</v>
+        <v>1204.640844496775</v>
       </c>
       <c r="E21">
-        <v>-60.346</v>
+        <v>-48.38</v>
       </c>
       <c r="F21">
-        <v>227.354</v>
+        <v>239.32</v>
       </c>
       <c r="G21">
         <v>62.4</v>
@@ -3015,45 +3015,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M21">
-        <v>12.163439</v>
+        <v>12.995076</v>
       </c>
       <c r="N21">
-        <v>81.36156099999999</v>
+        <v>80.52992399999999</v>
       </c>
       <c r="O21">
-        <v>12.20423415</v>
+        <v>12.0794886</v>
       </c>
       <c r="P21">
-        <v>69.15732684999999</v>
+        <v>68.45043539999999</v>
       </c>
       <c r="Q21">
-        <v>92.25732684999998</v>
+        <v>91.55043539999998</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08473606503444037</v>
+        <v>0.08516189693458544</v>
       </c>
       <c r="T21">
-        <v>0.7386027659371753</v>
+        <v>0.746680639728305</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.68902610519936</v>
+        <v>7.196956755004742</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07736051754766836</v>
+        <v>0.07731537241743999</v>
       </c>
       <c r="C22">
-        <v>1027.720844496775</v>
+        <v>1017.480468014177</v>
       </c>
       <c r="D22">
-        <v>1204.640844496775</v>
+        <v>1206.366468014177</v>
       </c>
       <c r="E22">
-        <v>-48.38</v>
+        <v>-36.41399999999999</v>
       </c>
       <c r="F22">
-        <v>239.32</v>
+        <v>251.286</v>
       </c>
       <c r="G22">
         <v>62.4</v>
@@ -3097,28 +3097,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M22">
-        <v>12.995076</v>
+        <v>13.6448298</v>
       </c>
       <c r="N22">
-        <v>80.52992399999999</v>
+        <v>79.88017019999999</v>
       </c>
       <c r="O22">
-        <v>12.0794886</v>
+        <v>11.98202553</v>
       </c>
       <c r="P22">
-        <v>68.45043539999999</v>
+        <v>67.89814466999999</v>
       </c>
       <c r="Q22">
-        <v>91.55043539999998</v>
+        <v>90.99814466999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08516189693458544</v>
+        <v>0.08559850938916455</v>
       </c>
       <c r="T22">
-        <v>0.746680639728305</v>
+        <v>0.7549630166533874</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.196956755004742</v>
+        <v>6.854244528575944</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07731537241743999</v>
+        <v>0.07727022728721164</v>
       </c>
       <c r="C23">
-        <v>1017.480468014177</v>
+        <v>1007.245042464898</v>
       </c>
       <c r="D23">
-        <v>1206.366468014177</v>
+        <v>1208.097042464898</v>
       </c>
       <c r="E23">
-        <v>-36.41400000000002</v>
+        <v>-24.44799999999998</v>
       </c>
       <c r="F23">
-        <v>251.286</v>
+        <v>263.252</v>
       </c>
       <c r="G23">
         <v>62.4</v>
@@ -3179,28 +3179,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M23">
-        <v>13.6448298</v>
+        <v>14.2945836</v>
       </c>
       <c r="N23">
-        <v>79.88017019999999</v>
+        <v>79.2304164</v>
       </c>
       <c r="O23">
-        <v>11.98202553</v>
+        <v>11.88456246</v>
       </c>
       <c r="P23">
-        <v>67.89814466999999</v>
+        <v>67.34585394</v>
       </c>
       <c r="Q23">
-        <v>90.99814466999999</v>
+        <v>90.44585393999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08559850938916455</v>
+        <v>0.08604631703488672</v>
       </c>
       <c r="T23">
-        <v>0.7549630166533873</v>
+        <v>0.7634577622175744</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.854244528575945</v>
+        <v>6.542687959095219</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07727022728721164</v>
+        <v>0.07722508215698329</v>
       </c>
       <c r="C24">
-        <v>1007.245042464898</v>
+        <v>997.0145891864022</v>
       </c>
       <c r="D24">
-        <v>1208.097042464898</v>
+        <v>1209.832589186402</v>
       </c>
       <c r="E24">
-        <v>-24.44799999999998</v>
+        <v>-12.48199999999997</v>
       </c>
       <c r="F24">
-        <v>263.252</v>
+        <v>275.218</v>
       </c>
       <c r="G24">
         <v>62.4</v>
@@ -3261,28 +3261,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M24">
-        <v>14.2945836</v>
+        <v>14.9443374</v>
       </c>
       <c r="N24">
-        <v>79.2304164</v>
+        <v>78.58066259999998</v>
       </c>
       <c r="O24">
-        <v>11.88456246</v>
+        <v>11.78709939</v>
       </c>
       <c r="P24">
-        <v>67.34585394</v>
+        <v>66.79356320999999</v>
       </c>
       <c r="Q24">
-        <v>90.44585393999999</v>
+        <v>89.89356320999998</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08604631703488672</v>
+        <v>0.08650575604803024</v>
       </c>
       <c r="T24">
-        <v>0.7634577622175744</v>
+        <v>0.7721731505236883</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.542687959095219</v>
+        <v>6.258223265221512</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07722508215698329</v>
+        <v>0.07738393702675495</v>
       </c>
       <c r="C25">
-        <v>997.0145891864022</v>
+        <v>978.9636037003334</v>
       </c>
       <c r="D25">
-        <v>1209.832589186402</v>
+        <v>1203.747603700333</v>
       </c>
       <c r="E25">
-        <v>-12.48199999999997</v>
+        <v>-0.5159999999999627</v>
       </c>
       <c r="F25">
-        <v>275.218</v>
+        <v>287.184</v>
       </c>
       <c r="G25">
         <v>62.4</v>
@@ -3343,45 +3343,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M25">
-        <v>14.9443374</v>
+        <v>15.8812752</v>
       </c>
       <c r="N25">
-        <v>78.58066259999998</v>
+        <v>77.64372479999999</v>
       </c>
       <c r="O25">
-        <v>11.78709939</v>
+        <v>11.64655872</v>
       </c>
       <c r="P25">
-        <v>66.79356320999999</v>
+        <v>65.99716607999999</v>
       </c>
       <c r="Q25">
-        <v>89.89356320999998</v>
+        <v>89.09716607999998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08650575604803024</v>
+        <v>0.08697728556151965</v>
       </c>
       <c r="T25">
-        <v>0.7721731505236883</v>
+        <v>0.7811178911536474</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.258223265221512</v>
+        <v>5.889010726292305</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07738393702675495</v>
+        <v>0.07734729189652659</v>
       </c>
       <c r="C26">
-        <v>978.9636037003334</v>
+        <v>968.3958691313049</v>
       </c>
       <c r="D26">
-        <v>1203.747603700333</v>
+        <v>1205.145869131305</v>
       </c>
       <c r="E26">
-        <v>-0.5160000000000196</v>
+        <v>11.44999999999999</v>
       </c>
       <c r="F26">
-        <v>287.184</v>
+        <v>299.15</v>
       </c>
       <c r="G26">
         <v>62.4</v>
@@ -3425,28 +3425,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M26">
-        <v>15.8812752</v>
+        <v>16.542995</v>
       </c>
       <c r="N26">
-        <v>77.64372479999999</v>
+        <v>76.98200499999999</v>
       </c>
       <c r="O26">
-        <v>11.64655872</v>
+        <v>11.54730075</v>
       </c>
       <c r="P26">
-        <v>65.99716607999999</v>
+        <v>65.43470424999998</v>
       </c>
       <c r="Q26">
-        <v>89.09716607999998</v>
+        <v>88.53470424999998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08697728556151965</v>
+        <v>0.08746138919536878</v>
       </c>
       <c r="T26">
-        <v>0.7811178911536474</v>
+        <v>0.7903011582004053</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.889010726292306</v>
+        <v>5.653450297240615</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07734729189652659</v>
+        <v>0.07731064676629823</v>
       </c>
       <c r="C27">
-        <v>968.3958691313049</v>
+        <v>957.831386772184</v>
       </c>
       <c r="D27">
-        <v>1205.145869131305</v>
+        <v>1206.547386772184</v>
       </c>
       <c r="E27">
-        <v>11.44999999999999</v>
+        <v>23.416</v>
       </c>
       <c r="F27">
-        <v>299.15</v>
+        <v>311.116</v>
       </c>
       <c r="G27">
         <v>62.4</v>
@@ -3507,28 +3507,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M27">
-        <v>16.542995</v>
+        <v>17.2047148</v>
       </c>
       <c r="N27">
-        <v>76.98200499999999</v>
+        <v>76.32028519999999</v>
       </c>
       <c r="O27">
-        <v>11.54730075</v>
+        <v>11.44804278</v>
       </c>
       <c r="P27">
-        <v>65.43470424999998</v>
+        <v>64.87224241999999</v>
       </c>
       <c r="Q27">
-        <v>88.53470424999998</v>
+        <v>87.97224241999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08746138919536878</v>
+        <v>0.08795857671121382</v>
       </c>
       <c r="T27">
-        <v>0.7903011582004053</v>
+        <v>0.7997326216538324</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.653450297240615</v>
+        <v>5.436009901192898</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07731064676629823</v>
+        <v>0.07727400163606989</v>
       </c>
       <c r="C28">
-        <v>957.831386772184</v>
+        <v>947.2701679825994</v>
       </c>
       <c r="D28">
-        <v>1206.547386772184</v>
+        <v>1207.952167982599</v>
       </c>
       <c r="E28">
-        <v>23.416</v>
+        <v>35.38200000000001</v>
       </c>
       <c r="F28">
-        <v>311.116</v>
+        <v>323.082</v>
       </c>
       <c r="G28">
         <v>62.4</v>
@@ -3589,28 +3589,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M28">
-        <v>17.2047148</v>
+        <v>17.8664346</v>
       </c>
       <c r="N28">
-        <v>76.32028519999999</v>
+        <v>75.65856539999999</v>
       </c>
       <c r="O28">
-        <v>11.44804278</v>
+        <v>11.34878481</v>
       </c>
       <c r="P28">
-        <v>64.87224241999999</v>
+        <v>64.30978058999999</v>
       </c>
       <c r="Q28">
-        <v>87.97224241999999</v>
+        <v>87.40978058999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08795857671121382</v>
+        <v>0.08846938580283545</v>
       </c>
       <c r="T28">
-        <v>0.7997326216538324</v>
+        <v>0.8094224813662576</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.436009901192898</v>
+        <v>5.234676201148716</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07727400163606989</v>
+        <v>0.07723735650584153</v>
       </c>
       <c r="C29">
-        <v>947.2701679825994</v>
+        <v>936.7122241751463</v>
       </c>
       <c r="D29">
-        <v>1207.952167982599</v>
+        <v>1209.360224175146</v>
       </c>
       <c r="E29">
-        <v>35.38200000000001</v>
+        <v>47.34800000000001</v>
       </c>
       <c r="F29">
-        <v>323.082</v>
+        <v>335.048</v>
       </c>
       <c r="G29">
         <v>62.4</v>
@@ -3671,28 +3671,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M29">
-        <v>17.8664346</v>
+        <v>18.5281544</v>
       </c>
       <c r="N29">
-        <v>75.65856539999999</v>
+        <v>74.99684559999999</v>
       </c>
       <c r="O29">
-        <v>11.34878481</v>
+        <v>11.24952684</v>
       </c>
       <c r="P29">
-        <v>64.30978058999999</v>
+        <v>63.74731875999998</v>
       </c>
       <c r="Q29">
-        <v>87.40978058999998</v>
+        <v>86.84731875999998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08846938580283545</v>
+        <v>0.08899438403589101</v>
       </c>
       <c r="T29">
-        <v>0.8094224813662576</v>
+        <v>0.8193815038484723</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.234676201148716</v>
+        <v>5.047723479679119</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07723735650584153</v>
+        <v>0.07720071137561317</v>
       </c>
       <c r="C30">
-        <v>936.7122241751463</v>
+        <v>926.1575668156926</v>
       </c>
       <c r="D30">
-        <v>1209.360224175146</v>
+        <v>1210.771566815692</v>
       </c>
       <c r="E30">
-        <v>47.34800000000001</v>
+        <v>59.31400000000002</v>
       </c>
       <c r="F30">
-        <v>335.048</v>
+        <v>347.014</v>
       </c>
       <c r="G30">
         <v>62.4</v>
@@ -3753,28 +3753,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M30">
-        <v>18.5281544</v>
+        <v>19.1898742</v>
       </c>
       <c r="N30">
-        <v>74.99684559999999</v>
+        <v>74.33512579999999</v>
       </c>
       <c r="O30">
-        <v>11.24952684</v>
+        <v>11.15026887</v>
       </c>
       <c r="P30">
-        <v>63.74731875999998</v>
+        <v>63.18485692999999</v>
       </c>
       <c r="Q30">
-        <v>86.84731875999998</v>
+        <v>86.28485692999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08899438403589101</v>
+        <v>0.08953417095156785</v>
       </c>
       <c r="T30">
-        <v>0.8193815038484723</v>
+        <v>0.8296210621752563</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.047723479679119</v>
+        <v>4.873664049345356</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07720071137561317</v>
+        <v>0.07716406624538481</v>
       </c>
       <c r="C31">
-        <v>926.1575668156927</v>
+        <v>915.6062074236934</v>
       </c>
       <c r="D31">
-        <v>1210.771566815692</v>
+        <v>1212.186207423693</v>
       </c>
       <c r="E31">
-        <v>59.31399999999996</v>
+        <v>71.27999999999997</v>
       </c>
       <c r="F31">
-        <v>347.014</v>
+        <v>358.98</v>
       </c>
       <c r="G31">
         <v>62.4</v>
@@ -3835,28 +3835,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M31">
-        <v>19.1898742</v>
+        <v>19.851594</v>
       </c>
       <c r="N31">
-        <v>74.33512579999999</v>
+        <v>73.673406</v>
       </c>
       <c r="O31">
-        <v>11.15026887</v>
+        <v>11.0510109</v>
       </c>
       <c r="P31">
-        <v>63.18485692999999</v>
+        <v>62.6223951</v>
       </c>
       <c r="Q31">
-        <v>86.28485692999999</v>
+        <v>85.7223951</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08953417095156785</v>
+        <v>0.09008938035054974</v>
       </c>
       <c r="T31">
-        <v>0.8296210621752563</v>
+        <v>0.8401531793113771</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.873664049345357</v>
+        <v>4.711208581033846</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07716406624538481</v>
+        <v>0.07712742111515647</v>
       </c>
       <c r="C32">
-        <v>915.6062074236934</v>
+        <v>905.058157572503</v>
       </c>
       <c r="D32">
-        <v>1212.186207423693</v>
+        <v>1213.604157572503</v>
       </c>
       <c r="E32">
-        <v>71.27999999999997</v>
+        <v>83.24599999999998</v>
       </c>
       <c r="F32">
-        <v>358.98</v>
+        <v>370.946</v>
       </c>
       <c r="G32">
         <v>62.4</v>
@@ -3917,28 +3917,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M32">
-        <v>19.851594</v>
+        <v>20.5133138</v>
       </c>
       <c r="N32">
-        <v>73.673406</v>
+        <v>73.01168619999999</v>
       </c>
       <c r="O32">
-        <v>11.0510109</v>
+        <v>10.95175293</v>
       </c>
       <c r="P32">
-        <v>62.6223951</v>
+        <v>62.05993326999999</v>
       </c>
       <c r="Q32">
-        <v>85.7223951</v>
+        <v>85.15993326999998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09008938035054974</v>
+        <v>0.09066068277558909</v>
       </c>
       <c r="T32">
-        <v>0.8401531793113771</v>
+        <v>0.8509905752050666</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.711208581033846</v>
+        <v>4.559234110677915</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07712742111515647</v>
+        <v>0.0777707759849281</v>
       </c>
       <c r="C33">
-        <v>905.058157572503</v>
+        <v>868.670537493045</v>
       </c>
       <c r="D33">
-        <v>1213.604157572503</v>
+        <v>1189.182537493045</v>
       </c>
       <c r="E33">
-        <v>83.24599999999998</v>
+        <v>95.21199999999999</v>
       </c>
       <c r="F33">
-        <v>370.946</v>
+        <v>382.912</v>
       </c>
       <c r="G33">
         <v>62.4</v>
@@ -3999,45 +3999,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M33">
-        <v>20.5133138</v>
+        <v>22.1323136</v>
       </c>
       <c r="N33">
-        <v>73.01168619999999</v>
+        <v>71.39268639999999</v>
       </c>
       <c r="O33">
-        <v>10.95175293</v>
+        <v>10.70890296</v>
       </c>
       <c r="P33">
-        <v>62.05993326999999</v>
+        <v>60.68378343999999</v>
       </c>
       <c r="Q33">
-        <v>85.15993326999998</v>
+        <v>83.78378343999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09066068277558909</v>
+        <v>0.09124878821312957</v>
       </c>
       <c r="T33">
-        <v>0.8509905752050666</v>
+        <v>0.8621467180368058</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.559234110677915</v>
+        <v>4.225721797110266</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0777707759849281</v>
+        <v>0.07775538085469977</v>
       </c>
       <c r="C34">
-        <v>868.670537493045</v>
+        <v>857.2774494578</v>
       </c>
       <c r="D34">
-        <v>1189.182537493045</v>
+        <v>1189.7554494578</v>
       </c>
       <c r="E34">
-        <v>95.21199999999999</v>
+        <v>107.178</v>
       </c>
       <c r="F34">
-        <v>382.912</v>
+        <v>394.878</v>
       </c>
       <c r="G34">
         <v>62.4</v>
@@ -4081,28 +4081,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M34">
-        <v>22.1323136</v>
+        <v>22.8239484</v>
       </c>
       <c r="N34">
-        <v>71.39268639999999</v>
+        <v>70.70105159999999</v>
       </c>
       <c r="O34">
-        <v>10.70890296</v>
+        <v>10.60515774</v>
       </c>
       <c r="P34">
-        <v>60.68378343999999</v>
+        <v>60.09589385999999</v>
       </c>
       <c r="Q34">
-        <v>83.78378343999998</v>
+        <v>83.19589385999998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09124878821312957</v>
+        <v>0.09185444903686532</v>
       </c>
       <c r="T34">
-        <v>0.8621467180368058</v>
+        <v>0.8736358800575522</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.225721797110266</v>
+        <v>4.097669621440257</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07775538085469977</v>
+        <v>0.07875148572447141</v>
       </c>
       <c r="C35">
-        <v>857.2774494578</v>
+        <v>809.3458117638936</v>
       </c>
       <c r="D35">
-        <v>1189.7554494578</v>
+        <v>1153.789811763894</v>
       </c>
       <c r="E35">
-        <v>107.178</v>
+        <v>119.144</v>
       </c>
       <c r="F35">
-        <v>394.878</v>
+        <v>406.844</v>
       </c>
       <c r="G35">
         <v>62.4</v>
@@ -4163,45 +4163,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M35">
-        <v>22.8239484</v>
+        <v>24.9395372</v>
       </c>
       <c r="N35">
-        <v>70.70105159999999</v>
+        <v>68.58546279999999</v>
       </c>
       <c r="O35">
-        <v>10.60515774</v>
+        <v>10.28781942</v>
       </c>
       <c r="P35">
-        <v>60.09589385999999</v>
+        <v>58.29764337999999</v>
       </c>
       <c r="Q35">
-        <v>83.19589385999998</v>
+        <v>81.39764337999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09185444903686532</v>
+        <v>0.09247846321889608</v>
       </c>
       <c r="T35">
-        <v>0.8736358800575522</v>
+        <v>0.8854731985031696</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.15</v>
       </c>
       <c r="W35">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.097669621440257</v>
+        <v>3.750069588300138</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07875148572447141</v>
+        <v>0.07876584059424305</v>
       </c>
       <c r="C36">
-        <v>809.3458117638936</v>
+        <v>796.8773976833438</v>
       </c>
       <c r="D36">
-        <v>1153.789811763894</v>
+        <v>1153.287397683344</v>
       </c>
       <c r="E36">
-        <v>119.144</v>
+        <v>131.11</v>
       </c>
       <c r="F36">
-        <v>406.844</v>
+        <v>418.81</v>
       </c>
       <c r="G36">
         <v>62.4</v>
@@ -4245,28 +4245,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M36">
-        <v>24.9395372</v>
+        <v>25.673053</v>
       </c>
       <c r="N36">
-        <v>68.58546279999999</v>
+        <v>67.851947</v>
       </c>
       <c r="O36">
-        <v>10.28781942</v>
+        <v>10.17779205</v>
       </c>
       <c r="P36">
-        <v>58.29764337999999</v>
+        <v>57.67415494999999</v>
       </c>
       <c r="Q36">
-        <v>81.39764337999998</v>
+        <v>80.77415495</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09247846321889608</v>
+        <v>0.09312167783729701</v>
       </c>
       <c r="T36">
-        <v>0.8854731985031696</v>
+        <v>0.8976747421317293</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.750069588300138</v>
+        <v>3.642924742920135</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07876584059424305</v>
+        <v>0.0787801954640147</v>
       </c>
       <c r="C37">
-        <v>796.8773976833438</v>
+        <v>784.4094209615535</v>
       </c>
       <c r="D37">
-        <v>1153.287397683344</v>
+        <v>1152.785420961553</v>
       </c>
       <c r="E37">
-        <v>131.11</v>
+        <v>143.076</v>
       </c>
       <c r="F37">
-        <v>418.81</v>
+        <v>430.776</v>
       </c>
       <c r="G37">
         <v>62.4</v>
@@ -4327,28 +4327,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M37">
-        <v>25.673053</v>
+        <v>26.4065688</v>
       </c>
       <c r="N37">
-        <v>67.851947</v>
+        <v>67.11843119999999</v>
       </c>
       <c r="O37">
-        <v>10.17779205</v>
+        <v>10.06776468</v>
       </c>
       <c r="P37">
-        <v>57.67415494999999</v>
+        <v>57.05066651999999</v>
       </c>
       <c r="Q37">
-        <v>80.77415495</v>
+        <v>80.15066651999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09312167783729701</v>
+        <v>0.09378499291252297</v>
       </c>
       <c r="T37">
-        <v>0.8976747421317293</v>
+        <v>0.9102575839986813</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.642924742920135</v>
+        <v>3.54173238895013</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07878019546401469</v>
+        <v>0.07967515033378635</v>
       </c>
       <c r="C38">
-        <v>784.409420961554</v>
+        <v>741.9877354184457</v>
       </c>
       <c r="D38">
-        <v>1152.785420961554</v>
+        <v>1122.329735418446</v>
       </c>
       <c r="E38">
-        <v>143.076</v>
+        <v>155.042</v>
       </c>
       <c r="F38">
-        <v>430.776</v>
+        <v>442.742</v>
       </c>
       <c r="G38">
         <v>62.4</v>
@@ -4409,45 +4409,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M38">
-        <v>26.4065688</v>
+        <v>28.3797622</v>
       </c>
       <c r="N38">
-        <v>67.11843119999999</v>
+        <v>65.14523779999999</v>
       </c>
       <c r="O38">
-        <v>10.06776468</v>
+        <v>9.771785669999998</v>
       </c>
       <c r="P38">
-        <v>57.05066651999999</v>
+        <v>55.37345212999999</v>
       </c>
       <c r="Q38">
-        <v>80.15066651999999</v>
+        <v>78.47345212999998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09378499291252296</v>
+        <v>0.09446936560918467</v>
       </c>
       <c r="T38">
-        <v>0.9102575839986811</v>
+        <v>0.9232398811629967</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.541732388950131</v>
+        <v>3.295482158761711</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07967515033378635</v>
+        <v>0.07971330520355799</v>
       </c>
       <c r="C39">
-        <v>741.9877354184457</v>
+        <v>728.7590349933854</v>
       </c>
       <c r="D39">
-        <v>1122.329735418446</v>
+        <v>1121.067034993385</v>
       </c>
       <c r="E39">
-        <v>155.042</v>
+        <v>167.008</v>
       </c>
       <c r="F39">
-        <v>442.742</v>
+        <v>454.708</v>
       </c>
       <c r="G39">
         <v>62.4</v>
@@ -4491,28 +4491,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M39">
-        <v>28.3797622</v>
+        <v>29.1467828</v>
       </c>
       <c r="N39">
-        <v>65.14523779999999</v>
+        <v>64.37821719999999</v>
       </c>
       <c r="O39">
-        <v>9.771785669999998</v>
+        <v>9.656732579999998</v>
       </c>
       <c r="P39">
-        <v>55.37345212999999</v>
+        <v>54.72148462</v>
       </c>
       <c r="Q39">
-        <v>78.47345212999998</v>
+        <v>77.82148461999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09446936560918467</v>
+        <v>0.09517581484444837</v>
       </c>
       <c r="T39">
-        <v>0.9232398811629967</v>
+        <v>0.9366409621068064</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.295482158761711</v>
+        <v>3.208758944057455</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07971330520355799</v>
+        <v>0.07975146007332964</v>
       </c>
       <c r="C40">
-        <v>728.7590349933854</v>
+        <v>715.5331726300853</v>
       </c>
       <c r="D40">
-        <v>1121.067034993385</v>
+        <v>1119.807172630085</v>
       </c>
       <c r="E40">
-        <v>167.008</v>
+        <v>178.974</v>
       </c>
       <c r="F40">
-        <v>454.708</v>
+        <v>466.674</v>
       </c>
       <c r="G40">
         <v>62.4</v>
@@ -4573,28 +4573,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M40">
-        <v>29.1467828</v>
+        <v>29.9138034</v>
       </c>
       <c r="N40">
-        <v>64.37821719999999</v>
+        <v>63.61119659999999</v>
       </c>
       <c r="O40">
-        <v>9.656732579999998</v>
+        <v>9.541679489999998</v>
       </c>
       <c r="P40">
-        <v>54.72148462</v>
+        <v>54.06951710999999</v>
       </c>
       <c r="Q40">
-        <v>77.82148461999999</v>
+        <v>77.16951710999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09517581484444837</v>
+        <v>0.09590542634972071</v>
       </c>
       <c r="T40">
-        <v>0.9366409621068064</v>
+        <v>0.9504814227536916</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.208758944057455</v>
+        <v>3.126483073697008</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07975146007332964</v>
+        <v>0.07978961494310129</v>
       </c>
       <c r="C41">
-        <v>715.5331726300853</v>
+        <v>702.3101387709913</v>
       </c>
       <c r="D41">
-        <v>1119.807172630085</v>
+        <v>1118.550138770991</v>
       </c>
       <c r="E41">
-        <v>178.974</v>
+        <v>190.94</v>
       </c>
       <c r="F41">
-        <v>466.674</v>
+        <v>478.64</v>
       </c>
       <c r="G41">
         <v>62.4</v>
@@ -4655,28 +4655,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M41">
-        <v>29.9138034</v>
+        <v>30.680824</v>
       </c>
       <c r="N41">
-        <v>63.61119659999999</v>
+        <v>62.84417599999999</v>
       </c>
       <c r="O41">
-        <v>9.541679489999998</v>
+        <v>9.426626399999998</v>
       </c>
       <c r="P41">
-        <v>54.06951710999999</v>
+        <v>53.41754959999999</v>
       </c>
       <c r="Q41">
-        <v>77.16951710999999</v>
+        <v>76.5175496</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09590542634972071</v>
+        <v>0.09665935823850215</v>
       </c>
       <c r="T41">
-        <v>0.9504814227536916</v>
+        <v>0.9647832320888067</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.126483073697008</v>
+        <v>3.048320996854582</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07978961494310129</v>
+        <v>0.08254606981287294</v>
       </c>
       <c r="C42">
-        <v>702.3101387709913</v>
+        <v>606.4376695131841</v>
       </c>
       <c r="D42">
-        <v>1118.550138770991</v>
+        <v>1034.643669513184</v>
       </c>
       <c r="E42">
-        <v>190.94</v>
+        <v>202.906</v>
       </c>
       <c r="F42">
-        <v>478.64</v>
+        <v>490.606</v>
       </c>
       <c r="G42">
         <v>62.4</v>
@@ -4737,45 +4737,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M42">
-        <v>30.680824</v>
+        <v>35.2745714</v>
       </c>
       <c r="N42">
-        <v>62.84417599999999</v>
+        <v>58.25042859999999</v>
       </c>
       <c r="O42">
-        <v>9.426626399999998</v>
+        <v>8.737564289999998</v>
       </c>
       <c r="P42">
-        <v>53.41754959999999</v>
+        <v>49.51286431</v>
       </c>
       <c r="Q42">
-        <v>76.5175496</v>
+        <v>72.61286430999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09665935823850215</v>
+        <v>0.09743884714046261</v>
       </c>
       <c r="T42">
-        <v>0.9647832320888067</v>
+        <v>0.979569848520027</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.048320996854582</v>
+        <v>2.651343341339648</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08254606981287294</v>
+        <v>0.08265052468264458</v>
       </c>
       <c r="C43">
-        <v>606.4376695131841</v>
+        <v>591.5389142623491</v>
       </c>
       <c r="D43">
-        <v>1034.643669513184</v>
+        <v>1031.710914262349</v>
       </c>
       <c r="E43">
-        <v>202.906</v>
+        <v>214.872</v>
       </c>
       <c r="F43">
-        <v>490.606</v>
+        <v>502.572</v>
       </c>
       <c r="G43">
         <v>62.4</v>
@@ -4819,28 +4819,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M43">
-        <v>35.2745714</v>
+        <v>36.1349268</v>
       </c>
       <c r="N43">
-        <v>58.25042859999999</v>
+        <v>57.39007319999999</v>
       </c>
       <c r="O43">
-        <v>8.737564289999998</v>
+        <v>8.608510979999998</v>
       </c>
       <c r="P43">
-        <v>49.51286431</v>
+        <v>48.78156221999999</v>
       </c>
       <c r="Q43">
-        <v>72.61286430999999</v>
+        <v>71.88156221999998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09743884714046261</v>
+        <v>0.09824521497007686</v>
       </c>
       <c r="T43">
-        <v>0.979569848520027</v>
+        <v>0.9948663482764619</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.651343341339648</v>
+        <v>2.588216118926799</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08265052468264458</v>
+        <v>0.08275497955241623</v>
       </c>
       <c r="C44">
-        <v>591.5389142623492</v>
+        <v>576.6567381340845</v>
       </c>
       <c r="D44">
-        <v>1031.710914262349</v>
+        <v>1028.794738134084</v>
       </c>
       <c r="E44">
-        <v>214.872</v>
+        <v>226.8379999999999</v>
       </c>
       <c r="F44">
-        <v>502.5719999999999</v>
+        <v>514.5379999999999</v>
       </c>
       <c r="G44">
         <v>62.4</v>
@@ -4901,28 +4901,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M44">
-        <v>36.1349268</v>
+        <v>36.9952822</v>
       </c>
       <c r="N44">
-        <v>57.39007319999999</v>
+        <v>56.52971779999999</v>
       </c>
       <c r="O44">
-        <v>8.608510979999998</v>
+        <v>8.479457669999999</v>
       </c>
       <c r="P44">
-        <v>48.78156221999999</v>
+        <v>48.05026013</v>
       </c>
       <c r="Q44">
-        <v>71.88156221999998</v>
+        <v>71.15026012999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09824521497007685</v>
+        <v>0.09907987640774776</v>
       </c>
       <c r="T44">
-        <v>0.9948663482764618</v>
+        <v>1.010699567322596</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.588216118926799</v>
+        <v>2.528025046393618</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08275497955241623</v>
+        <v>0.08431803442218788</v>
       </c>
       <c r="C45">
-        <v>576.6567381340845</v>
+        <v>522.9424337473573</v>
       </c>
       <c r="D45">
-        <v>1028.794738134084</v>
+        <v>987.0464337473572</v>
       </c>
       <c r="E45">
-        <v>226.8379999999999</v>
+        <v>238.804</v>
       </c>
       <c r="F45">
-        <v>514.5379999999999</v>
+        <v>526.504</v>
       </c>
       <c r="G45">
         <v>62.4</v>
@@ -4983,45 +4983,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M45">
-        <v>36.9952822</v>
+        <v>39.90900320000001</v>
       </c>
       <c r="N45">
-        <v>56.52971779999999</v>
+        <v>53.61599679999998</v>
       </c>
       <c r="O45">
-        <v>8.479457669999999</v>
+        <v>8.042399519999996</v>
       </c>
       <c r="P45">
-        <v>48.05026013</v>
+        <v>45.57359727999999</v>
       </c>
       <c r="Q45">
-        <v>71.15026012999999</v>
+        <v>68.67359727999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09907987640774776</v>
+        <v>0.09994434718247835</v>
       </c>
       <c r="T45">
-        <v>1.010699567322596</v>
+        <v>1.027098258477521</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.528025046393618</v>
+        <v>2.343456175322363</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08431803442218788</v>
+        <v>0.08445563929195953</v>
       </c>
       <c r="C46">
-        <v>522.9424337473573</v>
+        <v>507.4627835151484</v>
       </c>
       <c r="D46">
-        <v>987.0464337473572</v>
+        <v>983.5327835151485</v>
       </c>
       <c r="E46">
-        <v>238.804</v>
+        <v>250.77</v>
       </c>
       <c r="F46">
-        <v>526.504</v>
+        <v>538.47</v>
       </c>
       <c r="G46">
         <v>62.4</v>
@@ -5065,28 +5065,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M46">
-        <v>39.90900320000001</v>
+        <v>40.81602600000001</v>
       </c>
       <c r="N46">
-        <v>53.61599679999998</v>
+        <v>52.70897399999998</v>
       </c>
       <c r="O46">
-        <v>8.042399519999996</v>
+        <v>7.906346099999997</v>
       </c>
       <c r="P46">
-        <v>45.57359727999999</v>
+        <v>44.80262789999999</v>
       </c>
       <c r="Q46">
-        <v>68.67359727999998</v>
+        <v>67.90262789999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09994434718247835</v>
+        <v>0.1008402532581082</v>
       </c>
       <c r="T46">
-        <v>1.027098258477521</v>
+        <v>1.044093265674443</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.343456175322363</v>
+        <v>2.291379371426311</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08445563929195953</v>
+        <v>0.08459324416173117</v>
       </c>
       <c r="C47">
-        <v>507.4627835151484</v>
+        <v>492.0080600655832</v>
       </c>
       <c r="D47">
-        <v>983.5327835151485</v>
+        <v>980.0440600655833</v>
       </c>
       <c r="E47">
-        <v>250.77</v>
+        <v>262.736</v>
       </c>
       <c r="F47">
-        <v>538.47</v>
+        <v>550.436</v>
       </c>
       <c r="G47">
         <v>62.4</v>
@@ -5147,28 +5147,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M47">
-        <v>40.81602600000001</v>
+        <v>41.72304880000001</v>
       </c>
       <c r="N47">
-        <v>52.70897399999998</v>
+        <v>51.80195119999998</v>
       </c>
       <c r="O47">
-        <v>7.906346099999997</v>
+        <v>7.770292679999997</v>
       </c>
       <c r="P47">
-        <v>44.80262789999999</v>
+        <v>44.03165851999999</v>
       </c>
       <c r="Q47">
-        <v>67.90262789999998</v>
+        <v>67.13165851999997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1008402532581082</v>
+        <v>0.1017693410402429</v>
       </c>
       <c r="T47">
-        <v>1.044093265674443</v>
+        <v>1.061717717582363</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.291379371426311</v>
+        <v>2.241566776395304</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08459324416173117</v>
+        <v>0.08473084903150281</v>
       </c>
       <c r="C48">
-        <v>492.0080600655832</v>
+        <v>476.5779990802532</v>
       </c>
       <c r="D48">
-        <v>980.0440600655833</v>
+        <v>976.5799990802533</v>
       </c>
       <c r="E48">
-        <v>262.736</v>
+        <v>274.7020000000001</v>
       </c>
       <c r="F48">
-        <v>550.436</v>
+        <v>562.402</v>
       </c>
       <c r="G48">
         <v>62.4</v>
@@ -5229,28 +5229,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M48">
-        <v>41.72304880000001</v>
+        <v>42.63007160000001</v>
       </c>
       <c r="N48">
-        <v>51.80195119999998</v>
+        <v>50.89492839999998</v>
       </c>
       <c r="O48">
-        <v>7.770292679999997</v>
+        <v>7.634239259999998</v>
       </c>
       <c r="P48">
-        <v>44.03165851999999</v>
+        <v>43.26068913999998</v>
       </c>
       <c r="Q48">
-        <v>67.13165851999997</v>
+        <v>66.36068913999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1017693410402429</v>
+        <v>0.1027334887386845</v>
       </c>
       <c r="T48">
-        <v>1.061717717582363</v>
+        <v>1.080007243147185</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.241566776395304</v>
+        <v>2.193873866259234</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08473084903150281</v>
+        <v>0.08486845390127445</v>
       </c>
       <c r="C49">
-        <v>476.5779990802532</v>
+        <v>461.1723399646249</v>
       </c>
       <c r="D49">
-        <v>976.5799990802533</v>
+        <v>973.1403399646249</v>
       </c>
       <c r="E49">
-        <v>274.7020000000001</v>
+        <v>286.6680000000001</v>
       </c>
       <c r="F49">
-        <v>562.402</v>
+        <v>574.3680000000001</v>
       </c>
       <c r="G49">
         <v>62.4</v>
@@ -5311,28 +5311,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M49">
-        <v>42.63007160000001</v>
+        <v>43.53709440000001</v>
       </c>
       <c r="N49">
-        <v>50.89492839999998</v>
+        <v>49.98790559999998</v>
       </c>
       <c r="O49">
-        <v>7.634239259999998</v>
+        <v>7.498185839999997</v>
       </c>
       <c r="P49">
-        <v>43.26068913999998</v>
+        <v>42.48971975999999</v>
       </c>
       <c r="Q49">
-        <v>66.36068913999998</v>
+        <v>65.58971975999998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1027334887386845</v>
+        <v>0.1037347190409124</v>
       </c>
       <c r="T49">
-        <v>1.080007243147185</v>
+        <v>1.099000212002961</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.193873866259234</v>
+        <v>2.148168160712167</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08486845390127445</v>
+        <v>0.08500605877104611</v>
       </c>
       <c r="C50">
-        <v>461.1723399646251</v>
+        <v>445.7908257826876</v>
       </c>
       <c r="D50">
-        <v>973.1403399646249</v>
+        <v>969.7248257826875</v>
       </c>
       <c r="E50">
-        <v>286.6679999999999</v>
+        <v>298.634</v>
       </c>
       <c r="F50">
-        <v>574.3679999999999</v>
+        <v>586.3339999999999</v>
       </c>
       <c r="G50">
         <v>62.4</v>
@@ -5393,28 +5393,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M50">
-        <v>43.5370944</v>
+        <v>44.4441172</v>
       </c>
       <c r="N50">
-        <v>49.98790559999999</v>
+        <v>49.08088279999999</v>
       </c>
       <c r="O50">
-        <v>7.498185839999998</v>
+        <v>7.362132419999998</v>
       </c>
       <c r="P50">
-        <v>42.48971975999999</v>
+        <v>41.71875037999999</v>
       </c>
       <c r="Q50">
-        <v>65.58971975999998</v>
+        <v>64.81875037999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1037347190409124</v>
+        <v>0.104775213276561</v>
       </c>
       <c r="T50">
-        <v>1.099000212002961</v>
+        <v>1.118738003166807</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.148168160712167</v>
+        <v>2.104327994167021</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08500605877104611</v>
+        <v>0.08514366364081777</v>
       </c>
       <c r="C51">
-        <v>445.7908257826876</v>
+        <v>430.4332031929771</v>
       </c>
       <c r="D51">
-        <v>969.7248257826875</v>
+        <v>966.333203192977</v>
       </c>
       <c r="E51">
-        <v>298.634</v>
+        <v>310.6</v>
       </c>
       <c r="F51">
-        <v>586.3339999999999</v>
+        <v>598.3</v>
       </c>
       <c r="G51">
         <v>62.4</v>
@@ -5475,28 +5475,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M51">
-        <v>44.4441172</v>
+        <v>45.35114</v>
       </c>
       <c r="N51">
-        <v>49.08088279999999</v>
+        <v>48.17385999999999</v>
       </c>
       <c r="O51">
-        <v>7.362132419999998</v>
+        <v>7.226078999999999</v>
       </c>
       <c r="P51">
-        <v>41.71875037999999</v>
+        <v>40.94778099999999</v>
       </c>
       <c r="Q51">
-        <v>64.81875037999998</v>
+        <v>64.04778099999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.104775213276561</v>
+        <v>0.1058573272816355</v>
       </c>
       <c r="T51">
-        <v>1.118738003166807</v>
+        <v>1.139265305977208</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.104327994167021</v>
+        <v>2.06224143428368</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08514366364081777</v>
+        <v>0.0852812685105894</v>
       </c>
       <c r="C52">
-        <v>430.4332031929771</v>
+        <v>415.0992223859342</v>
       </c>
       <c r="D52">
-        <v>966.333203192977</v>
+        <v>962.9652223859342</v>
       </c>
       <c r="E52">
-        <v>310.6</v>
+        <v>322.566</v>
       </c>
       <c r="F52">
-        <v>598.3</v>
+        <v>610.266</v>
       </c>
       <c r="G52">
         <v>62.4</v>
@@ -5557,28 +5557,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M52">
-        <v>45.35114</v>
+        <v>46.2581628</v>
       </c>
       <c r="N52">
-        <v>48.17385999999999</v>
+        <v>47.26683719999999</v>
       </c>
       <c r="O52">
-        <v>7.226078999999999</v>
+        <v>7.090025579999998</v>
       </c>
       <c r="P52">
-        <v>40.94778099999999</v>
+        <v>40.17681162</v>
       </c>
       <c r="Q52">
-        <v>64.04778099999999</v>
+        <v>63.27681161999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1058573272816355</v>
+        <v>0.1069836092052845</v>
       </c>
       <c r="T52">
-        <v>1.139265305977208</v>
+        <v>1.16063045788191</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.06224143428368</v>
+        <v>2.021805327729099</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0852812685105894</v>
+        <v>0.09169527338036106</v>
       </c>
       <c r="C53">
-        <v>415.0992223859342</v>
+        <v>268.5558864015475</v>
       </c>
       <c r="D53">
-        <v>962.9652223859342</v>
+        <v>828.3878864015475</v>
       </c>
       <c r="E53">
-        <v>322.566</v>
+        <v>334.532</v>
       </c>
       <c r="F53">
-        <v>610.266</v>
+        <v>622.232</v>
       </c>
       <c r="G53">
         <v>62.4</v>
@@ -5639,45 +5639,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M53">
-        <v>46.2581628</v>
+        <v>56.00088</v>
       </c>
       <c r="N53">
-        <v>47.26683719999999</v>
+        <v>37.52412</v>
       </c>
       <c r="O53">
-        <v>7.090025579999998</v>
+        <v>5.628617999999999</v>
       </c>
       <c r="P53">
-        <v>40.17681162</v>
+        <v>31.895502</v>
       </c>
       <c r="Q53">
-        <v>63.27681161999999</v>
+        <v>54.99550199999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1069836092052845</v>
+        <v>0.1081568195424189</v>
       </c>
       <c r="T53">
-        <v>1.16063045788191</v>
+        <v>1.182885824449308</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.15</v>
       </c>
       <c r="W53">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.021805327729099</v>
+        <v>1.670063041866485</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09169527338036106</v>
+        <v>0.0919535782501327</v>
       </c>
       <c r="C54">
-        <v>268.5558864015475</v>
+        <v>251.9536992795502</v>
       </c>
       <c r="D54">
-        <v>828.3878864015475</v>
+        <v>823.7516992795502</v>
       </c>
       <c r="E54">
-        <v>334.532</v>
+        <v>346.498</v>
       </c>
       <c r="F54">
-        <v>622.232</v>
+        <v>634.198</v>
       </c>
       <c r="G54">
         <v>62.4</v>
@@ -5721,28 +5721,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M54">
-        <v>56.00088</v>
+        <v>57.07782</v>
       </c>
       <c r="N54">
-        <v>37.52412</v>
+        <v>36.44718</v>
       </c>
       <c r="O54">
-        <v>5.628617999999999</v>
+        <v>5.467076999999999</v>
       </c>
       <c r="P54">
-        <v>31.895502</v>
+        <v>30.980103</v>
       </c>
       <c r="Q54">
-        <v>54.99550199999999</v>
+        <v>54.08010299999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1081568195424189</v>
+        <v>0.1093799537236866</v>
       </c>
       <c r="T54">
-        <v>1.182885824449308</v>
+        <v>1.206088227891914</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.670063041866485</v>
+        <v>1.638552418435042</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0919535782501327</v>
+        <v>0.09221188311990433</v>
       </c>
       <c r="C55">
-        <v>251.9536992795502</v>
+        <v>235.4031174633619</v>
       </c>
       <c r="D55">
-        <v>823.7516992795502</v>
+        <v>819.1671174633619</v>
       </c>
       <c r="E55">
-        <v>346.498</v>
+        <v>358.464</v>
       </c>
       <c r="F55">
-        <v>634.198</v>
+        <v>646.164</v>
       </c>
       <c r="G55">
         <v>62.4</v>
@@ -5803,28 +5803,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M55">
-        <v>57.07782</v>
+        <v>58.15476</v>
       </c>
       <c r="N55">
-        <v>36.44718</v>
+        <v>35.37024</v>
       </c>
       <c r="O55">
-        <v>5.467076999999999</v>
+        <v>5.305535999999999</v>
       </c>
       <c r="P55">
-        <v>30.980103</v>
+        <v>30.064704</v>
       </c>
       <c r="Q55">
-        <v>54.08010299999999</v>
+        <v>53.16470399999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1093799537236866</v>
+        <v>0.110656267651966</v>
       </c>
       <c r="T55">
-        <v>1.206088227891914</v>
+        <v>1.2302994314842</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.638552418435042</v>
+        <v>1.608208855130689</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09221188311990433</v>
+        <v>0.09247018798967599</v>
       </c>
       <c r="C56">
-        <v>235.4031174633619</v>
+        <v>218.9032840953796</v>
       </c>
       <c r="D56">
-        <v>819.1671174633619</v>
+        <v>814.6332840953796</v>
       </c>
       <c r="E56">
-        <v>358.464</v>
+        <v>370.43</v>
       </c>
       <c r="F56">
-        <v>646.164</v>
+        <v>658.13</v>
       </c>
       <c r="G56">
         <v>62.4</v>
@@ -5885,28 +5885,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M56">
-        <v>58.15476</v>
+        <v>59.2317</v>
       </c>
       <c r="N56">
-        <v>35.37024</v>
+        <v>34.2933</v>
       </c>
       <c r="O56">
-        <v>5.305535999999999</v>
+        <v>5.143994999999999</v>
       </c>
       <c r="P56">
-        <v>30.064704</v>
+        <v>29.14930499999999</v>
       </c>
       <c r="Q56">
-        <v>53.16470399999999</v>
+        <v>52.24930499999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.110656267651966</v>
+        <v>0.1119893066437244</v>
       </c>
       <c r="T56">
-        <v>1.2302994314842</v>
+        <v>1.255586688569475</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.608208855130689</v>
+        <v>1.578968694128313</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09247018798967599</v>
+        <v>0.09272849285944763</v>
       </c>
       <c r="C57">
-        <v>218.9032840953796</v>
+        <v>202.4533611833414</v>
       </c>
       <c r="D57">
-        <v>814.6332840953796</v>
+        <v>810.1493611833414</v>
       </c>
       <c r="E57">
-        <v>370.43</v>
+        <v>382.396</v>
       </c>
       <c r="F57">
-        <v>658.13</v>
+        <v>670.096</v>
       </c>
       <c r="G57">
         <v>62.4</v>
@@ -5967,28 +5967,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M57">
-        <v>59.2317</v>
+        <v>60.30864</v>
       </c>
       <c r="N57">
-        <v>34.2933</v>
+        <v>33.21635999999999</v>
       </c>
       <c r="O57">
-        <v>5.143994999999999</v>
+        <v>4.982453999999999</v>
       </c>
       <c r="P57">
-        <v>29.14930499999999</v>
+        <v>28.233906</v>
       </c>
       <c r="Q57">
-        <v>52.24930499999999</v>
+        <v>51.33390599999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1119893066437244</v>
+        <v>0.1133829383169264</v>
       </c>
       <c r="T57">
-        <v>1.255586688569475</v>
+        <v>1.282023366431354</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.578968694128313</v>
+        <v>1.550772824590307</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09272849285944763</v>
+        <v>0.09298679772921928</v>
       </c>
       <c r="C58">
-        <v>202.4533611833414</v>
+        <v>186.0525290839709</v>
       </c>
       <c r="D58">
-        <v>810.1493611833414</v>
+        <v>805.7145290839709</v>
       </c>
       <c r="E58">
-        <v>382.396</v>
+        <v>394.362</v>
       </c>
       <c r="F58">
-        <v>670.096</v>
+        <v>682.062</v>
       </c>
       <c r="G58">
         <v>62.4</v>
@@ -6049,28 +6049,28 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M58">
-        <v>60.30864</v>
+        <v>61.38558</v>
       </c>
       <c r="N58">
-        <v>33.21635999999999</v>
+        <v>32.13941999999999</v>
       </c>
       <c r="O58">
-        <v>4.982453999999999</v>
+        <v>4.820912999999999</v>
       </c>
       <c r="P58">
-        <v>28.233906</v>
+        <v>27.318507</v>
       </c>
       <c r="Q58">
-        <v>51.33390599999999</v>
+        <v>50.41850699999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1133829383169264</v>
+        <v>0.1148413900679518</v>
       </c>
       <c r="T58">
-        <v>1.282023366431354</v>
+        <v>1.309689657217042</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.550772824590307</v>
+        <v>1.523566283808021</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09298679772921928</v>
+        <v>0.122526961613142</v>
       </c>
       <c r="C59">
-        <v>186.0525290839709</v>
+        <v>-136.1165433744781</v>
       </c>
       <c r="D59">
-        <v>805.7145290839709</v>
+        <v>495.511456625522</v>
       </c>
       <c r="E59">
-        <v>394.362</v>
+        <v>406.328</v>
       </c>
       <c r="F59">
-        <v>682.062</v>
+        <v>694.028</v>
       </c>
       <c r="G59">
         <v>62.4</v>
@@ -6131,45 +6131,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M59">
-        <v>61.38558</v>
+        <v>101.8833104</v>
       </c>
       <c r="N59">
-        <v>32.13941999999999</v>
+        <v>-8.358310400000022</v>
       </c>
       <c r="O59">
-        <v>4.820912999999999</v>
+        <v>-1.253746560000003</v>
       </c>
       <c r="P59">
-        <v>27.318507</v>
+        <v>-7.104563840000019</v>
       </c>
       <c r="Q59">
-        <v>50.41850699999999</v>
+        <v>15.99543615999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1148413900679518</v>
+        <v>0.1169209623024873</v>
       </c>
       <c r="T59">
-        <v>1.309689657217042</v>
+        <v>1.349138374056698</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.15</v>
+        <v>0.1376942891325604</v>
       </c>
       <c r="W59">
-        <v>0.0765</v>
+        <v>0.1265864783553401</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.523566283808021</v>
+        <v>0.9179619275504026</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.122526961613142</v>
+        <v>0.1235369616131419</v>
       </c>
       <c r="C60">
-        <v>-136.1165433744777</v>
+        <v>-154.5204920774684</v>
       </c>
       <c r="D60">
-        <v>495.5114566255222</v>
+        <v>489.0735079225315</v>
       </c>
       <c r="E60">
-        <v>406.3279999999999</v>
+        <v>418.2939999999999</v>
       </c>
       <c r="F60">
-        <v>694.0279999999999</v>
+        <v>705.9939999999999</v>
       </c>
       <c r="G60">
         <v>62.4</v>
@@ -6213,37 +6213,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M60">
-        <v>101.8833104</v>
+        <v>103.6399192</v>
       </c>
       <c r="N60">
-        <v>-8.358310400000008</v>
+        <v>-10.1149192</v>
       </c>
       <c r="O60">
-        <v>-1.253746560000001</v>
+        <v>-1.51723788</v>
       </c>
       <c r="P60">
-        <v>-7.104563840000006</v>
+        <v>-8.597681320000003</v>
       </c>
       <c r="Q60">
-        <v>15.99543615999999</v>
+        <v>14.50231867999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1169209623024873</v>
+        <v>0.1186556199196211</v>
       </c>
       <c r="T60">
-        <v>1.349138374056697</v>
+        <v>1.38204418805808</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1376942891325604</v>
+        <v>0.1353604876218391</v>
       </c>
       <c r="W60">
-        <v>0.1265864783553401</v>
+        <v>0.126929080417114</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9179619275504027</v>
+        <v>0.9024032508122604</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1235369616131419</v>
+        <v>0.124546961613142</v>
       </c>
       <c r="C61">
-        <v>-154.5204920774684</v>
+        <v>-172.7592959150115</v>
       </c>
       <c r="D61">
-        <v>489.0735079225315</v>
+        <v>482.8007040849884</v>
       </c>
       <c r="E61">
-        <v>418.2939999999999</v>
+        <v>430.2599999999999</v>
       </c>
       <c r="F61">
-        <v>705.9939999999999</v>
+        <v>717.9599999999999</v>
       </c>
       <c r="G61">
         <v>62.4</v>
@@ -6295,37 +6295,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M61">
-        <v>103.6399192</v>
+        <v>105.396528</v>
       </c>
       <c r="N61">
-        <v>-10.1149192</v>
+        <v>-11.87152800000001</v>
       </c>
       <c r="O61">
-        <v>-1.51723788</v>
+        <v>-1.780729200000002</v>
       </c>
       <c r="P61">
-        <v>-8.597681320000003</v>
+        <v>-10.09079880000001</v>
       </c>
       <c r="Q61">
-        <v>14.50231867999999</v>
+        <v>13.00920119999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1186556199196211</v>
+        <v>0.1204770104176117</v>
       </c>
       <c r="T61">
-        <v>1.38204418805808</v>
+        <v>1.416595292759532</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1353604876218391</v>
+        <v>0.1331044794948084</v>
       </c>
       <c r="W61">
-        <v>0.126929080417114</v>
+        <v>0.1272602624101621</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9024032508122604</v>
+        <v>0.8873631966320559</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.124546961613142</v>
+        <v>0.1255569616131419</v>
       </c>
       <c r="C62">
-        <v>-172.7592959150115</v>
+        <v>-190.8392288089332</v>
       </c>
       <c r="D62">
-        <v>482.8007040849884</v>
+        <v>476.6867711910668</v>
       </c>
       <c r="E62">
-        <v>430.2599999999999</v>
+        <v>442.2259999999999</v>
       </c>
       <c r="F62">
-        <v>717.9599999999999</v>
+        <v>729.9259999999999</v>
       </c>
       <c r="G62">
         <v>62.4</v>
@@ -6377,37 +6377,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M62">
-        <v>105.396528</v>
+        <v>107.1531368</v>
       </c>
       <c r="N62">
-        <v>-11.87152800000001</v>
+        <v>-13.62813680000001</v>
       </c>
       <c r="O62">
-        <v>-1.780729200000002</v>
+        <v>-2.044220520000001</v>
       </c>
       <c r="P62">
-        <v>-10.09079880000001</v>
+        <v>-11.58391628000001</v>
       </c>
       <c r="Q62">
-        <v>13.00920119999998</v>
+        <v>11.51608371999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1204770104176117</v>
+        <v>0.1223918055565248</v>
       </c>
       <c r="T62">
-        <v>1.416595292759532</v>
+        <v>1.452918248984135</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1331044794948084</v>
+        <v>0.1309224388473525</v>
       </c>
       <c r="W62">
-        <v>0.1272602624101621</v>
+        <v>0.1275805859772086</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8873631966320559</v>
+        <v>0.8728162589823502</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1255569616131419</v>
+        <v>0.126566961613142</v>
       </c>
       <c r="C63">
-        <v>-190.8392288089332</v>
+        <v>-208.7662508566493</v>
       </c>
       <c r="D63">
-        <v>476.6867711910668</v>
+        <v>470.7257491433506</v>
       </c>
       <c r="E63">
-        <v>442.2259999999999</v>
+        <v>454.192</v>
       </c>
       <c r="F63">
-        <v>729.9259999999999</v>
+        <v>741.8919999999999</v>
       </c>
       <c r="G63">
         <v>62.4</v>
@@ -6459,37 +6459,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M63">
-        <v>107.1531368</v>
+        <v>108.9097456</v>
       </c>
       <c r="N63">
-        <v>-13.62813680000001</v>
+        <v>-15.38474560000002</v>
       </c>
       <c r="O63">
-        <v>-2.044220520000001</v>
+        <v>-2.307711840000002</v>
       </c>
       <c r="P63">
-        <v>-11.58391628000001</v>
+        <v>-13.07703376000001</v>
       </c>
       <c r="Q63">
-        <v>11.51608371999999</v>
+        <v>10.02296623999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1223918055565248</v>
+        <v>0.1244073793869596</v>
       </c>
       <c r="T63">
-        <v>1.452918248984135</v>
+        <v>1.491152939746876</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1309224388473525</v>
+        <v>0.1288107866078791</v>
       </c>
       <c r="W63">
-        <v>0.1275805859772086</v>
+        <v>0.1278905765259634</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8728162589823502</v>
+        <v>0.8587385773858606</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.126566961613142</v>
+        <v>0.127576961613142</v>
       </c>
       <c r="C64">
-        <v>-208.7662508566493</v>
+        <v>-226.5460277108677</v>
       </c>
       <c r="D64">
-        <v>470.7257491433506</v>
+        <v>464.9119722891322</v>
       </c>
       <c r="E64">
-        <v>454.192</v>
+        <v>466.158</v>
       </c>
       <c r="F64">
-        <v>741.8919999999999</v>
+        <v>753.8579999999999</v>
       </c>
       <c r="G64">
         <v>62.4</v>
@@ -6541,37 +6541,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M64">
-        <v>108.9097456</v>
+        <v>110.6663544</v>
       </c>
       <c r="N64">
-        <v>-15.38474560000002</v>
+        <v>-17.14135440000001</v>
       </c>
       <c r="O64">
-        <v>-2.307711840000002</v>
+        <v>-2.571203160000002</v>
       </c>
       <c r="P64">
-        <v>-13.07703376000001</v>
+        <v>-14.57015124000001</v>
       </c>
       <c r="Q64">
-        <v>10.02296623999998</v>
+        <v>8.529848759999984</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1244073793869596</v>
+        <v>0.1265319031541748</v>
       </c>
       <c r="T64">
-        <v>1.491152939746876</v>
+        <v>1.531454370550845</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1288107866078791</v>
+        <v>0.1267661709474366</v>
       </c>
       <c r="W64">
-        <v>0.1278905765259634</v>
+        <v>0.1281907261049163</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8587385773858606</v>
+        <v>0.8451078063162437</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.127576961613142</v>
+        <v>0.128586961613142</v>
       </c>
       <c r="C65">
-        <v>-226.5460277108677</v>
+        <v>-244.1839485406989</v>
       </c>
       <c r="D65">
-        <v>464.9119722891322</v>
+        <v>459.240051459301</v>
       </c>
       <c r="E65">
-        <v>466.158</v>
+        <v>478.124</v>
       </c>
       <c r="F65">
-        <v>753.8579999999999</v>
+        <v>765.824</v>
       </c>
       <c r="G65">
         <v>62.4</v>
@@ -6623,37 +6623,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M65">
-        <v>110.6663544</v>
+        <v>112.4229632</v>
       </c>
       <c r="N65">
-        <v>-17.14135440000001</v>
+        <v>-18.89796320000001</v>
       </c>
       <c r="O65">
-        <v>-2.571203160000002</v>
+        <v>-2.834694480000001</v>
       </c>
       <c r="P65">
-        <v>-14.57015124000001</v>
+        <v>-16.06326872000001</v>
       </c>
       <c r="Q65">
-        <v>8.529848759999984</v>
+        <v>7.036731279999987</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1265319031541748</v>
+        <v>0.1287744560195685</v>
       </c>
       <c r="T65">
-        <v>1.531454370550845</v>
+        <v>1.573994769732814</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1267661709474366</v>
+        <v>0.1247854495263829</v>
       </c>
       <c r="W65">
-        <v>0.1281907261049163</v>
+        <v>0.128481496009527</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8451078063162437</v>
+        <v>0.8319029968425524</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.128586961613142</v>
+        <v>0.129596961613142</v>
       </c>
       <c r="C66">
-        <v>-244.1839485406989</v>
+        <v>-261.6851426938621</v>
       </c>
       <c r="D66">
-        <v>459.240051459301</v>
+        <v>453.7048573061379</v>
       </c>
       <c r="E66">
-        <v>478.124</v>
+        <v>490.09</v>
       </c>
       <c r="F66">
-        <v>765.824</v>
+        <v>777.79</v>
       </c>
       <c r="G66">
         <v>62.4</v>
@@ -6705,37 +6705,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M66">
-        <v>112.4229632</v>
+        <v>114.179572</v>
       </c>
       <c r="N66">
-        <v>-18.89796320000001</v>
+        <v>-20.65457200000002</v>
       </c>
       <c r="O66">
-        <v>-2.834694480000001</v>
+        <v>-3.098185800000002</v>
       </c>
       <c r="P66">
-        <v>-16.06326872000001</v>
+        <v>-17.55638620000001</v>
       </c>
       <c r="Q66">
-        <v>7.036731279999987</v>
+        <v>5.543613799999981</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1287744560195685</v>
+        <v>0.1311451547629848</v>
       </c>
       <c r="T66">
-        <v>1.573994769732814</v>
+        <v>1.618966048868037</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1247854495263829</v>
+        <v>0.1228656733798231</v>
       </c>
       <c r="W66">
-        <v>0.128481496009527</v>
+        <v>0.128763319147842</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8319029968425524</v>
+        <v>0.8191044891988208</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.129596961613142</v>
+        <v>0.1306069616131419</v>
       </c>
       <c r="C67">
-        <v>-261.6851426938621</v>
+        <v>-279.0544951682677</v>
       </c>
       <c r="D67">
-        <v>453.7048573061379</v>
+        <v>448.3015048317323</v>
       </c>
       <c r="E67">
-        <v>490.09</v>
+        <v>502.056</v>
       </c>
       <c r="F67">
-        <v>777.79</v>
+        <v>789.756</v>
       </c>
       <c r="G67">
         <v>62.4</v>
@@ -6787,37 +6787,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M67">
-        <v>114.179572</v>
+        <v>115.9361808</v>
       </c>
       <c r="N67">
-        <v>-20.65457200000002</v>
+        <v>-22.41118080000001</v>
       </c>
       <c r="O67">
-        <v>-3.098185800000002</v>
+        <v>-3.361677120000002</v>
       </c>
       <c r="P67">
-        <v>-17.55638620000001</v>
+        <v>-19.04950368000001</v>
       </c>
       <c r="Q67">
-        <v>5.543613799999981</v>
+        <v>4.050496319999986</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1311451547629848</v>
+        <v>0.1336553063736608</v>
       </c>
       <c r="T67">
-        <v>1.618966048868037</v>
+        <v>1.666582697364156</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1228656733798231</v>
+        <v>0.1210040722680076</v>
       </c>
       <c r="W67">
-        <v>0.128763319147842</v>
+        <v>0.1290366021910565</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8191044891988208</v>
+        <v>0.8066938151200509</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1306069616131419</v>
+        <v>0.1684941790593586</v>
       </c>
       <c r="C68">
-        <v>-279.0544951682677</v>
+        <v>-429.4532775972434</v>
       </c>
       <c r="D68">
-        <v>448.3015048317323</v>
+        <v>309.8687224027566</v>
       </c>
       <c r="E68">
-        <v>502.056</v>
+        <v>514.0219999999999</v>
       </c>
       <c r="F68">
-        <v>789.756</v>
+        <v>801.722</v>
       </c>
       <c r="G68">
         <v>62.4</v>
@@ -6869,45 +6869,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M68">
-        <v>115.9361808</v>
+        <v>160.9857776</v>
       </c>
       <c r="N68">
-        <v>-22.41118080000001</v>
+        <v>-67.46077760000001</v>
       </c>
       <c r="O68">
-        <v>-3.361677120000002</v>
+        <v>-10.11911664</v>
       </c>
       <c r="P68">
-        <v>-19.04950368000001</v>
+        <v>-57.34166096000001</v>
       </c>
       <c r="Q68">
-        <v>4.050496319999986</v>
+        <v>-34.24166096000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1336553063736608</v>
+        <v>0.1384303685250343</v>
       </c>
       <c r="T68">
-        <v>1.666582697364156</v>
+        <v>1.757163861881081</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1210040722680076</v>
+        <v>0.08714279117784625</v>
       </c>
       <c r="W68">
-        <v>0.1290366021910565</v>
+        <v>0.1833017275314885</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8066938151200509</v>
+        <v>0.5809519411856416</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1684941790593586</v>
+        <v>0.1700441790593586</v>
       </c>
       <c r="C69">
-        <v>-429.4532775972434</v>
+        <v>-445.2850242532282</v>
       </c>
       <c r="D69">
-        <v>309.8687224027566</v>
+        <v>306.0029757467718</v>
       </c>
       <c r="E69">
-        <v>514.0219999999999</v>
+        <v>525.9880000000001</v>
       </c>
       <c r="F69">
-        <v>801.722</v>
+        <v>813.688</v>
       </c>
       <c r="G69">
         <v>62.4</v>
@@ -6951,37 +6951,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M69">
-        <v>160.9857776</v>
+        <v>163.3885504</v>
       </c>
       <c r="N69">
-        <v>-67.46077760000001</v>
+        <v>-69.86355040000002</v>
       </c>
       <c r="O69">
-        <v>-10.11911664</v>
+        <v>-10.47953256</v>
       </c>
       <c r="P69">
-        <v>-57.34166096000001</v>
+        <v>-59.38401784000002</v>
       </c>
       <c r="Q69">
-        <v>-34.24166096000002</v>
+        <v>-36.28401784000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1384303685250343</v>
+        <v>0.1413250675414416</v>
       </c>
       <c r="T69">
-        <v>1.757163861881081</v>
+        <v>1.812075232564865</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08714279117784625</v>
+        <v>0.08586127954287792</v>
       </c>
       <c r="W69">
-        <v>0.1833017275314885</v>
+        <v>0.1835590550677901</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5809519411856416</v>
+        <v>0.5724085302858528</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1700441790593586</v>
+        <v>0.1715941790593586</v>
       </c>
       <c r="C70">
-        <v>-445.2850242532282</v>
+        <v>-461.0215056535136</v>
       </c>
       <c r="D70">
-        <v>306.0029757467718</v>
+        <v>302.2324943464864</v>
       </c>
       <c r="E70">
-        <v>525.9880000000001</v>
+        <v>537.954</v>
       </c>
       <c r="F70">
-        <v>813.688</v>
+        <v>825.654</v>
       </c>
       <c r="G70">
         <v>62.4</v>
@@ -7033,37 +7033,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M70">
-        <v>163.3885504</v>
+        <v>165.7913232</v>
       </c>
       <c r="N70">
-        <v>-69.86355040000002</v>
+        <v>-72.2663232</v>
       </c>
       <c r="O70">
-        <v>-10.47953256</v>
+        <v>-10.83994848</v>
       </c>
       <c r="P70">
-        <v>-59.38401784000002</v>
+        <v>-61.42637472</v>
       </c>
       <c r="Q70">
-        <v>-36.28401784000003</v>
+        <v>-38.32637472</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1413250675414416</v>
+        <v>0.144406521333101</v>
       </c>
       <c r="T70">
-        <v>1.812075232564865</v>
+        <v>1.870529272325022</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08586127954287792</v>
+        <v>0.08461691317269129</v>
       </c>
       <c r="W70">
-        <v>0.1835590550677901</v>
+        <v>0.1838089238349236</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5724085302858528</v>
+        <v>0.5641127544846086</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1715941790593586</v>
+        <v>0.1731441790593586</v>
       </c>
       <c r="C71">
-        <v>-461.0215056535136</v>
+        <v>-476.666200429336</v>
       </c>
       <c r="D71">
-        <v>302.2324943464864</v>
+        <v>298.553799570664</v>
       </c>
       <c r="E71">
-        <v>537.954</v>
+        <v>549.9200000000001</v>
       </c>
       <c r="F71">
-        <v>825.654</v>
+        <v>837.62</v>
       </c>
       <c r="G71">
         <v>62.4</v>
@@ -7115,37 +7115,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M71">
-        <v>165.7913232</v>
+        <v>168.194096</v>
       </c>
       <c r="N71">
-        <v>-72.2663232</v>
+        <v>-74.66909600000001</v>
       </c>
       <c r="O71">
-        <v>-10.83994848</v>
+        <v>-11.2003644</v>
       </c>
       <c r="P71">
-        <v>-61.42637472</v>
+        <v>-63.46873160000001</v>
       </c>
       <c r="Q71">
-        <v>-38.32637472</v>
+        <v>-40.36873160000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.144406521333101</v>
+        <v>0.1476934053775377</v>
       </c>
       <c r="T71">
-        <v>1.870529272325022</v>
+        <v>1.93288024806919</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08461691317269129</v>
+        <v>0.08340810012736712</v>
       </c>
       <c r="W71">
-        <v>0.1838089238349236</v>
+        <v>0.1840516534944247</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5641127544846086</v>
+        <v>0.5560540008491142</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1731441790593586</v>
+        <v>0.1746941790593586</v>
       </c>
       <c r="C72">
-        <v>-476.666200429336</v>
+        <v>-492.2224198846415</v>
       </c>
       <c r="D72">
-        <v>298.553799570664</v>
+        <v>294.9635801153586</v>
       </c>
       <c r="E72">
-        <v>549.9200000000001</v>
+        <v>561.886</v>
       </c>
       <c r="F72">
-        <v>837.62</v>
+        <v>849.586</v>
       </c>
       <c r="G72">
         <v>62.4</v>
@@ -7197,37 +7197,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M72">
-        <v>168.194096</v>
+        <v>170.5968688</v>
       </c>
       <c r="N72">
-        <v>-74.66909600000001</v>
+        <v>-77.07186880000002</v>
       </c>
       <c r="O72">
-        <v>-11.2003644</v>
+        <v>-11.56078032</v>
       </c>
       <c r="P72">
-        <v>-63.46873160000001</v>
+        <v>-65.51108848000001</v>
       </c>
       <c r="Q72">
-        <v>-40.36873160000002</v>
+        <v>-42.41108848000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1476934053775377</v>
+        <v>0.1512069710802114</v>
       </c>
       <c r="T72">
-        <v>1.93288024806919</v>
+        <v>1.999531291106059</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08340810012736712</v>
+        <v>0.08223333815374223</v>
       </c>
       <c r="W72">
-        <v>0.1840516534944247</v>
+        <v>0.1842875456987286</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5560540008491142</v>
+        <v>0.5482222543582815</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1746941790593586</v>
+        <v>0.1762441790593586</v>
       </c>
       <c r="C73">
-        <v>-492.2224198846413</v>
+        <v>-507.6933179373997</v>
       </c>
       <c r="D73">
-        <v>294.9635801153586</v>
+        <v>291.4586820626002</v>
       </c>
       <c r="E73">
-        <v>561.886</v>
+        <v>573.8519999999999</v>
       </c>
       <c r="F73">
-        <v>849.5859999999999</v>
+        <v>861.5519999999999</v>
       </c>
       <c r="G73">
         <v>62.4</v>
@@ -7279,37 +7279,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M73">
-        <v>170.5968688</v>
+        <v>172.9996416</v>
       </c>
       <c r="N73">
-        <v>-77.07186879999999</v>
+        <v>-79.4746416</v>
       </c>
       <c r="O73">
-        <v>-11.56078032</v>
+        <v>-11.92119624</v>
       </c>
       <c r="P73">
-        <v>-65.51108848</v>
+        <v>-67.55344536</v>
       </c>
       <c r="Q73">
-        <v>-42.41108848</v>
+        <v>-44.45344536</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1512069710802114</v>
+        <v>0.1549715057616475</v>
       </c>
       <c r="T73">
-        <v>1.999531291106058</v>
+        <v>2.070943122931274</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08223333815374224</v>
+        <v>0.08109120845716249</v>
       </c>
       <c r="W73">
-        <v>0.1842875456987286</v>
+        <v>0.1845168853418018</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5482222543582816</v>
+        <v>0.5406080563810833</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1762441790593586</v>
+        <v>0.1777941790593586</v>
       </c>
       <c r="C74">
-        <v>-507.6933179373997</v>
+        <v>-523.0819003604765</v>
       </c>
       <c r="D74">
-        <v>291.4586820626002</v>
+        <v>288.0360996395234</v>
       </c>
       <c r="E74">
-        <v>573.8519999999999</v>
+        <v>585.818</v>
       </c>
       <c r="F74">
-        <v>861.5519999999999</v>
+        <v>873.5179999999999</v>
       </c>
       <c r="G74">
         <v>62.4</v>
@@ -7361,37 +7361,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M74">
-        <v>172.9996416</v>
+        <v>175.4024144</v>
       </c>
       <c r="N74">
-        <v>-79.4746416</v>
+        <v>-81.87741440000001</v>
       </c>
       <c r="O74">
-        <v>-11.92119624</v>
+        <v>-12.28161216</v>
       </c>
       <c r="P74">
-        <v>-67.55344536</v>
+        <v>-69.59580224000001</v>
       </c>
       <c r="Q74">
-        <v>-44.45344536</v>
+        <v>-46.49580224000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1549715057616475</v>
+        <v>0.1590148948639308</v>
       </c>
       <c r="T74">
-        <v>2.070943122931274</v>
+        <v>2.147644720076876</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08109120845716249</v>
+        <v>0.07998036998514656</v>
       </c>
       <c r="W74">
-        <v>0.1845168853418018</v>
+        <v>0.1847399417069826</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5406080563810833</v>
+        <v>0.5332024665676438</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1777941790593586</v>
+        <v>0.1793441790593586</v>
       </c>
       <c r="C75">
-        <v>-523.0819003604765</v>
+        <v>-538.3910333789725</v>
       </c>
       <c r="D75">
-        <v>288.0360996395234</v>
+        <v>284.6929666210275</v>
       </c>
       <c r="E75">
-        <v>585.818</v>
+        <v>597.7839999999999</v>
       </c>
       <c r="F75">
-        <v>873.5179999999999</v>
+        <v>885.4839999999999</v>
       </c>
       <c r="G75">
         <v>62.4</v>
@@ -7443,37 +7443,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M75">
-        <v>175.4024144</v>
+        <v>177.8051872</v>
       </c>
       <c r="N75">
-        <v>-81.87741440000001</v>
+        <v>-84.28018719999999</v>
       </c>
       <c r="O75">
-        <v>-12.28161216</v>
+        <v>-12.64202808</v>
       </c>
       <c r="P75">
-        <v>-69.59580224000001</v>
+        <v>-71.63815911999998</v>
       </c>
       <c r="Q75">
-        <v>-46.49580224000002</v>
+        <v>-48.53815911999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1590148948639308</v>
+        <v>0.1633693138971589</v>
       </c>
       <c r="T75">
-        <v>2.147644720076876</v>
+        <v>2.230246440079834</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.07998036998514656</v>
+        <v>0.07889955417453647</v>
       </c>
       <c r="W75">
-        <v>0.1847399417069826</v>
+        <v>0.1849569695217531</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5332024665676438</v>
+        <v>0.5259970278302433</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1793441790593586</v>
+        <v>0.1808941790593586</v>
       </c>
       <c r="C76">
-        <v>-538.3910333789725</v>
+        <v>-553.6234516757127</v>
       </c>
       <c r="D76">
-        <v>284.6929666210275</v>
+        <v>281.4265483242872</v>
       </c>
       <c r="E76">
-        <v>597.7839999999999</v>
+        <v>609.75</v>
       </c>
       <c r="F76">
-        <v>885.4839999999999</v>
+        <v>897.4499999999999</v>
       </c>
       <c r="G76">
         <v>62.4</v>
@@ -7525,37 +7525,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M76">
-        <v>177.8051872</v>
+        <v>180.20796</v>
       </c>
       <c r="N76">
-        <v>-84.28018719999999</v>
+        <v>-86.68295999999999</v>
       </c>
       <c r="O76">
-        <v>-12.64202808</v>
+        <v>-13.002444</v>
       </c>
       <c r="P76">
-        <v>-71.63815911999998</v>
+        <v>-73.680516</v>
       </c>
       <c r="Q76">
-        <v>-48.53815911999999</v>
+        <v>-50.580516</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1633693138971589</v>
+        <v>0.1680720864530452</v>
       </c>
       <c r="T76">
-        <v>2.230246440079834</v>
+        <v>2.319456297683027</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07889955417453647</v>
+        <v>0.07784756011887599</v>
       </c>
       <c r="W76">
-        <v>0.1849569695217531</v>
+        <v>0.1851682099281297</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5259970278302433</v>
+        <v>0.5189837341258399</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1808941790593586</v>
+        <v>0.1824441790593586</v>
       </c>
       <c r="C77">
-        <v>-553.6234516757127</v>
+        <v>-568.7817658518852</v>
       </c>
       <c r="D77">
-        <v>281.4265483242872</v>
+        <v>278.2342341481148</v>
       </c>
       <c r="E77">
-        <v>609.75</v>
+        <v>621.7159999999999</v>
       </c>
       <c r="F77">
-        <v>897.4499999999999</v>
+        <v>909.4159999999999</v>
       </c>
       <c r="G77">
         <v>62.4</v>
@@ -7607,37 +7607,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M77">
-        <v>180.20796</v>
+        <v>182.6107328</v>
       </c>
       <c r="N77">
-        <v>-86.68295999999999</v>
+        <v>-89.0857328</v>
       </c>
       <c r="O77">
-        <v>-13.002444</v>
+        <v>-13.36285992</v>
       </c>
       <c r="P77">
-        <v>-73.680516</v>
+        <v>-75.72287288</v>
       </c>
       <c r="Q77">
-        <v>-50.580516</v>
+        <v>-52.62287288</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1680720864530452</v>
+        <v>0.1731667567219221</v>
       </c>
       <c r="T77">
-        <v>2.319456297683027</v>
+        <v>2.416100310086487</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07784756011887599</v>
+        <v>0.07682325011731182</v>
       </c>
       <c r="W77">
-        <v>0.1851682099281297</v>
+        <v>0.1853738913764438</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5189837341258399</v>
+        <v>0.5121550007820789</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1824441790593586</v>
+        <v>0.1839941790593586</v>
       </c>
       <c r="C78">
-        <v>-568.7817658518852</v>
+        <v>-583.8684693856017</v>
       </c>
       <c r="D78">
-        <v>278.2342341481148</v>
+        <v>275.1135306143983</v>
       </c>
       <c r="E78">
-        <v>621.7159999999999</v>
+        <v>633.682</v>
       </c>
       <c r="F78">
-        <v>909.4159999999999</v>
+        <v>921.3819999999999</v>
       </c>
       <c r="G78">
         <v>62.4</v>
@@ -7689,37 +7689,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M78">
-        <v>182.6107328</v>
+        <v>185.0135056</v>
       </c>
       <c r="N78">
-        <v>-89.0857328</v>
+        <v>-91.48850560000001</v>
       </c>
       <c r="O78">
-        <v>-13.36285992</v>
+        <v>-13.72327584</v>
       </c>
       <c r="P78">
-        <v>-75.72287288</v>
+        <v>-77.76522976000001</v>
       </c>
       <c r="Q78">
-        <v>-52.62287288</v>
+        <v>-54.66522976000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1731667567219221</v>
+        <v>0.1787044417967883</v>
       </c>
       <c r="T78">
-        <v>2.416100310086487</v>
+        <v>2.521148149655464</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07682325011731182</v>
+        <v>0.07582554557033375</v>
       </c>
       <c r="W78">
-        <v>0.1853738913764438</v>
+        <v>0.185574230449477</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5121550007820789</v>
+        <v>0.5055036371355583</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1839941790593586</v>
+        <v>0.2131255147203598</v>
       </c>
       <c r="C79">
-        <v>-583.8684693856017</v>
+        <v>-643.731675132168</v>
       </c>
       <c r="D79">
-        <v>275.1135306143983</v>
+        <v>227.216324867832</v>
       </c>
       <c r="E79">
-        <v>633.682</v>
+        <v>645.6479999999999</v>
       </c>
       <c r="F79">
-        <v>921.3819999999999</v>
+        <v>933.348</v>
       </c>
       <c r="G79">
         <v>62.4</v>
@@ -7771,45 +7771,45 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M79">
-        <v>185.0135056</v>
+        <v>220.0834584</v>
       </c>
       <c r="N79">
-        <v>-91.48850560000001</v>
+        <v>-126.5584584</v>
       </c>
       <c r="O79">
-        <v>-13.72327584</v>
+        <v>-18.98376876</v>
       </c>
       <c r="P79">
-        <v>-77.76522976000001</v>
+        <v>-107.57468964</v>
       </c>
       <c r="Q79">
-        <v>-54.66522976000002</v>
+        <v>-84.47468964000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1787044417967883</v>
+        <v>0.186024351246648</v>
       </c>
       <c r="T79">
-        <v>2.521148149655464</v>
+        <v>2.660004127045418</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07582554557033375</v>
+        <v>0.06374286419337728</v>
       </c>
       <c r="W79">
-        <v>0.185574230449477</v>
+        <v>0.2207694326232016</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5055036371355583</v>
+        <v>0.4249524279558485</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2131255147203598</v>
+        <v>0.2150255147203598</v>
       </c>
       <c r="C80">
-        <v>-643.731675132168</v>
+        <v>-658.2487739895846</v>
       </c>
       <c r="D80">
-        <v>227.216324867832</v>
+        <v>224.6652260104153</v>
       </c>
       <c r="E80">
-        <v>645.6479999999999</v>
+        <v>657.614</v>
       </c>
       <c r="F80">
-        <v>933.348</v>
+        <v>945.314</v>
       </c>
       <c r="G80">
         <v>62.4</v>
@@ -7853,37 +7853,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M80">
-        <v>220.0834584</v>
+        <v>222.9050412</v>
       </c>
       <c r="N80">
-        <v>-126.5584584</v>
+        <v>-129.3800412</v>
       </c>
       <c r="O80">
-        <v>-18.98376876</v>
+        <v>-19.40700618</v>
       </c>
       <c r="P80">
-        <v>-107.57468964</v>
+        <v>-109.97303502</v>
       </c>
       <c r="Q80">
-        <v>-84.47468964000002</v>
+        <v>-86.87303502</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.186024351246648</v>
+        <v>0.1927017013060122</v>
       </c>
       <c r="T80">
-        <v>2.660004127045418</v>
+        <v>2.786670990238057</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06374286419337728</v>
+        <v>0.06293599249472694</v>
       </c>
       <c r="W80">
-        <v>0.2207694326232016</v>
+        <v>0.2209596929697434</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4249524279558485</v>
+        <v>0.4195732832981797</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2150255147203598</v>
+        <v>0.2169255147203598</v>
       </c>
       <c r="C81">
-        <v>-658.2487739895846</v>
+        <v>-672.7092233422562</v>
       </c>
       <c r="D81">
-        <v>224.6652260104153</v>
+        <v>222.1707766577437</v>
       </c>
       <c r="E81">
-        <v>657.614</v>
+        <v>669.5799999999999</v>
       </c>
       <c r="F81">
-        <v>945.314</v>
+        <v>957.28</v>
       </c>
       <c r="G81">
         <v>62.4</v>
@@ -7935,37 +7935,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M81">
-        <v>222.9050412</v>
+        <v>225.726624</v>
       </c>
       <c r="N81">
-        <v>-129.3800412</v>
+        <v>-132.201624</v>
       </c>
       <c r="O81">
-        <v>-19.40700618</v>
+        <v>-19.83024360000001</v>
       </c>
       <c r="P81">
-        <v>-109.97303502</v>
+        <v>-112.3713804</v>
       </c>
       <c r="Q81">
-        <v>-86.87303502</v>
+        <v>-89.27138040000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1927017013060122</v>
+        <v>0.2000467863713128</v>
       </c>
       <c r="T81">
-        <v>2.786670990238057</v>
+        <v>2.926004539749961</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06293599249472694</v>
+        <v>0.06214929258854284</v>
       </c>
       <c r="W81">
-        <v>0.2209596929697434</v>
+        <v>0.2211451968076216</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4195732832981797</v>
+        <v>0.4143286172569522</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2169255147203598</v>
+        <v>0.2188255147203599</v>
       </c>
       <c r="C82">
-        <v>-672.7092233422562</v>
+        <v>-687.1148894015189</v>
       </c>
       <c r="D82">
-        <v>222.1707766577437</v>
+        <v>219.7311105984811</v>
       </c>
       <c r="E82">
-        <v>669.5799999999999</v>
+        <v>681.546</v>
       </c>
       <c r="F82">
-        <v>957.28</v>
+        <v>969.246</v>
       </c>
       <c r="G82">
         <v>62.4</v>
@@ -8017,37 +8017,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M82">
-        <v>225.726624</v>
+        <v>228.5482068</v>
       </c>
       <c r="N82">
-        <v>-132.201624</v>
+        <v>-135.0232068</v>
       </c>
       <c r="O82">
-        <v>-19.83024360000001</v>
+        <v>-20.25348102</v>
       </c>
       <c r="P82">
-        <v>-112.3713804</v>
+        <v>-114.76972578</v>
       </c>
       <c r="Q82">
-        <v>-89.27138040000004</v>
+        <v>-91.66972578000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2000467863713128</v>
+        <v>0.2081650382855924</v>
       </c>
       <c r="T82">
-        <v>2.926004539749961</v>
+        <v>3.080004778684169</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06214929258854284</v>
+        <v>0.06138201737140035</v>
       </c>
       <c r="W82">
-        <v>0.2211451968076216</v>
+        <v>0.2213261203038238</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4143286172569522</v>
+        <v>0.4092134491426689</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2188255147203599</v>
+        <v>0.2207255147203599</v>
       </c>
       <c r="C83">
-        <v>-687.1148894015189</v>
+        <v>-701.467557297306</v>
       </c>
       <c r="D83">
-        <v>219.7311105984811</v>
+        <v>217.344442702694</v>
       </c>
       <c r="E83">
-        <v>681.546</v>
+        <v>693.5119999999999</v>
       </c>
       <c r="F83">
-        <v>969.246</v>
+        <v>981.212</v>
       </c>
       <c r="G83">
         <v>62.4</v>
@@ -8099,37 +8099,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M83">
-        <v>228.5482068</v>
+        <v>231.3697896</v>
       </c>
       <c r="N83">
-        <v>-135.0232068</v>
+        <v>-137.8447896</v>
       </c>
       <c r="O83">
-        <v>-20.25348102</v>
+        <v>-20.67671844</v>
       </c>
       <c r="P83">
-        <v>-114.76972578</v>
+        <v>-117.16807116</v>
       </c>
       <c r="Q83">
-        <v>-91.66972578000002</v>
+        <v>-94.06807116000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2081650382855924</v>
+        <v>0.2171853181903476</v>
       </c>
       <c r="T83">
-        <v>3.080004778684169</v>
+        <v>3.251116155277734</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06138201737140035</v>
+        <v>0.06063345618394424</v>
       </c>
       <c r="W83">
-        <v>0.2213261203038238</v>
+        <v>0.221502631031826</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4092134491426689</v>
+        <v>0.404223041226295</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2207255147203599</v>
+        <v>0.2226255147203598</v>
       </c>
       <c r="C84">
-        <v>-701.467557297306</v>
+        <v>-715.7689354342688</v>
       </c>
       <c r="D84">
-        <v>217.344442702694</v>
+        <v>215.0090645657312</v>
       </c>
       <c r="E84">
-        <v>693.5119999999999</v>
+        <v>705.4780000000001</v>
       </c>
       <c r="F84">
-        <v>981.212</v>
+        <v>993.178</v>
       </c>
       <c r="G84">
         <v>62.4</v>
@@ -8181,37 +8181,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M84">
-        <v>231.3697896</v>
+        <v>234.1913724</v>
       </c>
       <c r="N84">
-        <v>-137.8447896</v>
+        <v>-140.6663724</v>
       </c>
       <c r="O84">
-        <v>-20.67671844</v>
+        <v>-21.09995586</v>
       </c>
       <c r="P84">
-        <v>-117.16807116</v>
+        <v>-119.56641654</v>
       </c>
       <c r="Q84">
-        <v>-94.06807116000002</v>
+        <v>-96.46641654000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2171853181903476</v>
+        <v>0.2272668074956621</v>
       </c>
       <c r="T84">
-        <v>3.251116155277734</v>
+        <v>3.442358282058777</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06063345618394424</v>
+        <v>0.05990293261546298</v>
       </c>
       <c r="W84">
-        <v>0.221502631031826</v>
+        <v>0.2216748884892738</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.404223041226295</v>
+        <v>0.3993528841030867</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2226255147203598</v>
+        <v>0.2245255147203598</v>
       </c>
       <c r="C85">
-        <v>-715.7689354342688</v>
+        <v>-730.0206595700424</v>
       </c>
       <c r="D85">
-        <v>215.0090645657312</v>
+        <v>212.7233404299576</v>
       </c>
       <c r="E85">
-        <v>705.4780000000001</v>
+        <v>717.444</v>
       </c>
       <c r="F85">
-        <v>993.178</v>
+        <v>1005.144</v>
       </c>
       <c r="G85">
         <v>62.4</v>
@@ -8263,37 +8263,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M85">
-        <v>234.1913724</v>
+        <v>237.0129552</v>
       </c>
       <c r="N85">
-        <v>-140.6663724</v>
+        <v>-143.4879552</v>
       </c>
       <c r="O85">
-        <v>-21.09995586</v>
+        <v>-21.52319328</v>
       </c>
       <c r="P85">
-        <v>-119.56641654</v>
+        <v>-121.96476192</v>
       </c>
       <c r="Q85">
-        <v>-96.46641654000001</v>
+        <v>-98.86476192000005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2272668074956621</v>
+        <v>0.2386084829641411</v>
       </c>
       <c r="T85">
-        <v>3.442358282058777</v>
+        <v>3.657505674687452</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05990293261546298</v>
+        <v>0.05918980246527889</v>
       </c>
       <c r="W85">
-        <v>0.2216748884892738</v>
+        <v>0.2218430445786872</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3993528841030867</v>
+        <v>0.3945986831018593</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2245255147203598</v>
+        <v>0.2264255147203598</v>
       </c>
       <c r="C86">
-        <v>-730.0206595700424</v>
+        <v>-744.2242966361162</v>
       </c>
       <c r="D86">
-        <v>212.7233404299575</v>
+        <v>210.4857033638837</v>
       </c>
       <c r="E86">
-        <v>717.444</v>
+        <v>729.4099999999999</v>
       </c>
       <c r="F86">
-        <v>1005.144</v>
+        <v>1017.11</v>
       </c>
       <c r="G86">
         <v>62.4</v>
@@ -8345,37 +8345,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M86">
-        <v>237.0129552</v>
+        <v>239.834538</v>
       </c>
       <c r="N86">
-        <v>-143.4879552</v>
+        <v>-146.309538</v>
       </c>
       <c r="O86">
-        <v>-21.52319328</v>
+        <v>-21.9464307</v>
       </c>
       <c r="P86">
-        <v>-121.96476192</v>
+        <v>-124.3631073</v>
       </c>
       <c r="Q86">
-        <v>-98.86476191999999</v>
+        <v>-101.2631073</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2386084829641409</v>
+        <v>0.251462381828417</v>
       </c>
       <c r="T86">
-        <v>3.657505674687449</v>
+        <v>3.901339386333279</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0591898024652789</v>
+        <v>0.05849345184804033</v>
       </c>
       <c r="W86">
-        <v>0.2218430445786872</v>
+        <v>0.2220072440542321</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3945986831018594</v>
+        <v>0.3899563456536023</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2264255147203598</v>
+        <v>0.2283255147203598</v>
       </c>
       <c r="C87">
-        <v>-744.2242966361162</v>
+        <v>-758.3813483200634</v>
       </c>
       <c r="D87">
-        <v>210.4857033638837</v>
+        <v>208.2946516799365</v>
       </c>
       <c r="E87">
-        <v>729.4099999999999</v>
+        <v>741.3759999999997</v>
       </c>
       <c r="F87">
-        <v>1017.11</v>
+        <v>1029.076</v>
       </c>
       <c r="G87">
         <v>62.4</v>
@@ -8427,37 +8427,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M87">
-        <v>239.834538</v>
+        <v>242.6561208</v>
       </c>
       <c r="N87">
-        <v>-146.309538</v>
+        <v>-149.1311208</v>
       </c>
       <c r="O87">
-        <v>-21.9464307</v>
+        <v>-22.36966811999999</v>
       </c>
       <c r="P87">
-        <v>-124.3631073</v>
+        <v>-126.76145268</v>
       </c>
       <c r="Q87">
-        <v>-101.2631073</v>
+        <v>-103.66145268</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.251462381828417</v>
+        <v>0.2661525519590182</v>
       </c>
       <c r="T87">
-        <v>3.901339386333279</v>
+        <v>4.180006485357085</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05849345184804033</v>
+        <v>0.05781329543120266</v>
       </c>
       <c r="W87">
-        <v>0.2220072440542321</v>
+        <v>0.2221676249373224</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3899563456536023</v>
+        <v>0.3854219695413511</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2283255147203598</v>
+        <v>0.2302255147203598</v>
       </c>
       <c r="C88">
-        <v>-758.3813483200634</v>
+        <v>-772.4932544263413</v>
       </c>
       <c r="D88">
-        <v>208.2946516799365</v>
+        <v>206.1487455736587</v>
       </c>
       <c r="E88">
-        <v>741.3759999999997</v>
+        <v>753.3419999999999</v>
       </c>
       <c r="F88">
-        <v>1029.076</v>
+        <v>1041.042</v>
       </c>
       <c r="G88">
         <v>62.4</v>
@@ -8509,37 +8509,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M88">
-        <v>242.6561208</v>
+        <v>245.4777036</v>
       </c>
       <c r="N88">
-        <v>-149.1311208</v>
+        <v>-151.9527036</v>
       </c>
       <c r="O88">
-        <v>-22.36966811999999</v>
+        <v>-22.79290554</v>
       </c>
       <c r="P88">
-        <v>-126.76145268</v>
+        <v>-129.15979806</v>
       </c>
       <c r="Q88">
-        <v>-103.66145268</v>
+        <v>-106.05979806</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2661525519590182</v>
+        <v>0.283102748263558</v>
       </c>
       <c r="T88">
-        <v>4.180006485357085</v>
+        <v>4.501545445769168</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05781329543120266</v>
+        <v>0.05714877479406239</v>
       </c>
       <c r="W88">
-        <v>0.2221676249373224</v>
+        <v>0.2223243189035601</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3854219695413511</v>
+        <v>0.3809918319604159</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2302255147203598</v>
+        <v>0.2321255147203598</v>
       </c>
       <c r="C89">
-        <v>-772.4932544263413</v>
+        <v>-786.5613960314661</v>
       </c>
       <c r="D89">
-        <v>206.1487455736587</v>
+        <v>204.0466039685339</v>
       </c>
       <c r="E89">
-        <v>753.3419999999999</v>
+        <v>765.308</v>
       </c>
       <c r="F89">
-        <v>1041.042</v>
+        <v>1053.008</v>
       </c>
       <c r="G89">
         <v>62.4</v>
@@ -8591,37 +8591,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M89">
-        <v>245.4777036</v>
+        <v>248.2992864</v>
       </c>
       <c r="N89">
-        <v>-151.9527036</v>
+        <v>-154.7742864000001</v>
       </c>
       <c r="O89">
-        <v>-22.79290554</v>
+        <v>-23.21614296000001</v>
       </c>
       <c r="P89">
-        <v>-129.15979806</v>
+        <v>-131.55814344</v>
       </c>
       <c r="Q89">
-        <v>-106.05979806</v>
+        <v>-108.45814344</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.283102748263558</v>
+        <v>0.3028779772855212</v>
       </c>
       <c r="T89">
-        <v>4.501545445769168</v>
+        <v>4.876674232916599</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05714877479406239</v>
+        <v>0.05649935689867531</v>
       </c>
       <c r="W89">
-        <v>0.2223243189035601</v>
+        <v>0.2224774516432924</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3809918319604159</v>
+        <v>0.376662379324502</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2321255147203598</v>
+        <v>0.2340255147203598</v>
       </c>
       <c r="C90">
-        <v>-786.5613960314661</v>
+        <v>-800.5870984480923</v>
       </c>
       <c r="D90">
-        <v>204.0466039685339</v>
+        <v>201.9869015519077</v>
       </c>
       <c r="E90">
-        <v>765.308</v>
+        <v>777.2739999999999</v>
       </c>
       <c r="F90">
-        <v>1053.008</v>
+        <v>1064.974</v>
       </c>
       <c r="G90">
         <v>62.4</v>
@@ -8673,37 +8673,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M90">
-        <v>248.2992864</v>
+        <v>251.1208692</v>
       </c>
       <c r="N90">
-        <v>-154.7742864000001</v>
+        <v>-157.5958692</v>
       </c>
       <c r="O90">
-        <v>-23.21614296000001</v>
+        <v>-23.63938038</v>
       </c>
       <c r="P90">
-        <v>-131.55814344</v>
+        <v>-133.95648882</v>
       </c>
       <c r="Q90">
-        <v>-108.45814344</v>
+        <v>-110.85648882</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3028779772855212</v>
+        <v>0.3262487024932959</v>
       </c>
       <c r="T90">
-        <v>4.876674232916599</v>
+        <v>5.320008254090836</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05649935689867531</v>
+        <v>0.05586453266385875</v>
       </c>
       <c r="W90">
-        <v>0.2224774516432924</v>
+        <v>0.2226271431978621</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.376662379324502</v>
+        <v>0.3724302177590584</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2340255147203598</v>
+        <v>0.2359255147203599</v>
       </c>
       <c r="C91">
-        <v>-800.5870984480923</v>
+        <v>-814.5716340113652</v>
       </c>
       <c r="D91">
-        <v>201.9869015519077</v>
+        <v>199.9683659886349</v>
       </c>
       <c r="E91">
-        <v>777.2739999999999</v>
+        <v>789.24</v>
       </c>
       <c r="F91">
-        <v>1064.974</v>
+        <v>1076.94</v>
       </c>
       <c r="G91">
         <v>62.4</v>
@@ -8755,37 +8755,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M91">
-        <v>251.1208692</v>
+        <v>253.942452</v>
       </c>
       <c r="N91">
-        <v>-157.5958692</v>
+        <v>-160.417452</v>
       </c>
       <c r="O91">
-        <v>-23.63938038</v>
+        <v>-24.0626178</v>
       </c>
       <c r="P91">
-        <v>-133.95648882</v>
+        <v>-136.3548342</v>
       </c>
       <c r="Q91">
-        <v>-110.85648882</v>
+        <v>-113.2548342</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3262487024932959</v>
+        <v>0.3542935727426256</v>
       </c>
       <c r="T91">
-        <v>5.320008254090836</v>
+        <v>5.852009079499921</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05586453266385875</v>
+        <v>0.05524381563426031</v>
       </c>
       <c r="W91">
-        <v>0.2226271431978621</v>
+        <v>0.2227735082734414</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3724302177590584</v>
+        <v>0.3682921042284021</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2359255147203599</v>
+        <v>0.2378255147203598</v>
       </c>
       <c r="C92">
-        <v>-814.5716340113652</v>
+        <v>-828.516224699856</v>
       </c>
       <c r="D92">
-        <v>199.9683659886349</v>
+        <v>197.9897753001439</v>
       </c>
       <c r="E92">
-        <v>789.24</v>
+        <v>801.2059999999999</v>
       </c>
       <c r="F92">
-        <v>1076.94</v>
+        <v>1088.906</v>
       </c>
       <c r="G92">
         <v>62.4</v>
@@ -8837,37 +8837,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M92">
-        <v>253.942452</v>
+        <v>256.7640348</v>
       </c>
       <c r="N92">
-        <v>-160.417452</v>
+        <v>-163.2390348</v>
       </c>
       <c r="O92">
-        <v>-24.0626178</v>
+        <v>-24.48585522</v>
       </c>
       <c r="P92">
-        <v>-136.3548342</v>
+        <v>-138.75317958</v>
       </c>
       <c r="Q92">
-        <v>-113.2548342</v>
+        <v>-115.65317958</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3542935727426256</v>
+        <v>0.3885706363806951</v>
       </c>
       <c r="T92">
-        <v>5.852009079499921</v>
+        <v>6.502232310555468</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05524381563426031</v>
+        <v>0.05463674073718053</v>
       </c>
       <c r="W92">
-        <v>0.2227735082734414</v>
+        <v>0.2229166565341728</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3682921042284021</v>
+        <v>0.3642449382478702</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2378255147203598</v>
+        <v>0.2397255147203599</v>
       </c>
       <c r="C93">
-        <v>-828.516224699856</v>
+        <v>-842.4220446024242</v>
       </c>
       <c r="D93">
-        <v>197.9897753001439</v>
+        <v>196.0499553975758</v>
       </c>
       <c r="E93">
-        <v>801.2059999999999</v>
+        <v>813.172</v>
       </c>
       <c r="F93">
-        <v>1088.906</v>
+        <v>1100.872</v>
       </c>
       <c r="G93">
         <v>62.4</v>
@@ -8919,37 +8919,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M93">
-        <v>256.7640348</v>
+        <v>259.5856176</v>
       </c>
       <c r="N93">
-        <v>-163.2390348</v>
+        <v>-166.0606176000001</v>
       </c>
       <c r="O93">
-        <v>-24.48585522</v>
+        <v>-24.90909264000001</v>
       </c>
       <c r="P93">
-        <v>-138.75317958</v>
+        <v>-141.15152496</v>
       </c>
       <c r="Q93">
-        <v>-115.65317958</v>
+        <v>-118.0515249600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3885706363806951</v>
+        <v>0.4314169659282821</v>
       </c>
       <c r="T93">
-        <v>6.502232310555468</v>
+        <v>7.315011349374903</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05463674073718053</v>
+        <v>0.05404286312047203</v>
       </c>
       <c r="W93">
-        <v>0.2229166565341728</v>
+        <v>0.2230566928761927</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3642449382478702</v>
+        <v>0.3602857541364802</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2397255147203599</v>
+        <v>0.2416255147203598</v>
       </c>
       <c r="C94">
-        <v>-842.4220446024242</v>
+        <v>-856.2902222414683</v>
       </c>
       <c r="D94">
-        <v>196.0499553975758</v>
+        <v>194.1477777585316</v>
       </c>
       <c r="E94">
-        <v>813.172</v>
+        <v>825.1379999999999</v>
       </c>
       <c r="F94">
-        <v>1100.872</v>
+        <v>1112.838</v>
       </c>
       <c r="G94">
         <v>62.4</v>
@@ -9001,37 +9001,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M94">
-        <v>259.5856176</v>
+        <v>262.4072004</v>
       </c>
       <c r="N94">
-        <v>-166.0606176000001</v>
+        <v>-168.8822004</v>
       </c>
       <c r="O94">
-        <v>-24.90909264000001</v>
+        <v>-25.33233006000001</v>
       </c>
       <c r="P94">
-        <v>-141.15152496</v>
+        <v>-143.54987034</v>
       </c>
       <c r="Q94">
-        <v>-118.0515249600001</v>
+        <v>-120.44987034</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4314169659282821</v>
+        <v>0.4865051039180368</v>
       </c>
       <c r="T94">
-        <v>7.315011349374903</v>
+        <v>8.360012970714177</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05404286312047203</v>
+        <v>0.05346175706541319</v>
       </c>
       <c r="W94">
-        <v>0.2230566928761927</v>
+        <v>0.2231937176839756</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3602857541364802</v>
+        <v>0.3564117137694213</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2416255147203598</v>
+        <v>0.2435255147203599</v>
       </c>
       <c r="C95">
-        <v>-856.2902222414683</v>
+        <v>-870.121842762234</v>
       </c>
       <c r="D95">
-        <v>194.1477777585316</v>
+        <v>192.2821572377661</v>
       </c>
       <c r="E95">
-        <v>825.1379999999999</v>
+        <v>837.104</v>
       </c>
       <c r="F95">
-        <v>1112.838</v>
+        <v>1124.804</v>
       </c>
       <c r="G95">
         <v>62.4</v>
@@ -9083,37 +9083,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M95">
-        <v>262.4072004</v>
+        <v>265.2287832</v>
       </c>
       <c r="N95">
-        <v>-168.8822004</v>
+        <v>-171.7037832</v>
       </c>
       <c r="O95">
-        <v>-25.33233006000001</v>
+        <v>-25.75556748</v>
       </c>
       <c r="P95">
-        <v>-143.54987034</v>
+        <v>-145.94821572</v>
       </c>
       <c r="Q95">
-        <v>-120.44987034</v>
+        <v>-122.84821572</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4865051039180368</v>
+        <v>0.5599559545710429</v>
       </c>
       <c r="T95">
-        <v>8.360012970714177</v>
+        <v>9.753348465833207</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05346175706541319</v>
+        <v>0.05289301496897263</v>
       </c>
       <c r="W95">
-        <v>0.2231937176839756</v>
+        <v>0.2233278270703163</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3564117137694213</v>
+        <v>0.3526200997931509</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2435255147203599</v>
+        <v>0.2454255147203598</v>
       </c>
       <c r="C96">
-        <v>-870.121842762234</v>
+        <v>-883.9179499970907</v>
       </c>
       <c r="D96">
-        <v>192.2821572377661</v>
+        <v>190.4520500029093</v>
       </c>
       <c r="E96">
-        <v>837.104</v>
+        <v>849.0699999999999</v>
       </c>
       <c r="F96">
-        <v>1124.804</v>
+        <v>1136.77</v>
       </c>
       <c r="G96">
         <v>62.4</v>
@@ -9165,37 +9165,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M96">
-        <v>265.2287832</v>
+        <v>268.050366</v>
       </c>
       <c r="N96">
-        <v>-171.7037832</v>
+        <v>-174.525366</v>
       </c>
       <c r="O96">
-        <v>-25.75556748</v>
+        <v>-26.1788049</v>
       </c>
       <c r="P96">
-        <v>-145.94821572</v>
+        <v>-148.3465611</v>
       </c>
       <c r="Q96">
-        <v>-122.84821572</v>
+        <v>-125.2465611</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5599559545710429</v>
+        <v>0.6627871454852517</v>
       </c>
       <c r="T96">
-        <v>9.753348465833207</v>
+        <v>11.70401815899985</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05289301496897263</v>
+        <v>0.05233624639035187</v>
       </c>
       <c r="W96">
-        <v>0.2233278270703163</v>
+        <v>0.223459113101155</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3526200997931509</v>
+        <v>0.3489083092690124</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2454255147203598</v>
+        <v>0.2473255147203599</v>
       </c>
       <c r="C97">
-        <v>-883.9179499970907</v>
+        <v>-897.6795484130415</v>
       </c>
       <c r="D97">
-        <v>190.4520500029093</v>
+        <v>188.6564515869586</v>
       </c>
       <c r="E97">
-        <v>849.0699999999999</v>
+        <v>861.0360000000001</v>
       </c>
       <c r="F97">
-        <v>1136.77</v>
+        <v>1148.736</v>
       </c>
       <c r="G97">
         <v>62.4</v>
@@ -9247,37 +9247,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M97">
-        <v>268.050366</v>
+        <v>270.8719488</v>
       </c>
       <c r="N97">
-        <v>-174.525366</v>
+        <v>-177.3469488000001</v>
       </c>
       <c r="O97">
-        <v>-26.1788049</v>
+        <v>-26.60204232000001</v>
       </c>
       <c r="P97">
-        <v>-148.3465611</v>
+        <v>-150.7449064800001</v>
       </c>
       <c r="Q97">
-        <v>-125.2465611</v>
+        <v>-127.6449064800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6627871454852517</v>
+        <v>0.817033931856565</v>
       </c>
       <c r="T97">
-        <v>11.70401815899985</v>
+        <v>14.63002269874982</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05233624639035187</v>
+        <v>0.05179107715711903</v>
       </c>
       <c r="W97">
-        <v>0.223459113101155</v>
+        <v>0.2235876640063513</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3489083092690124</v>
+        <v>0.3452738477141268</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2473255147203598</v>
+        <v>0.2492255147203598</v>
       </c>
       <c r="C98">
-        <v>-897.6795484130411</v>
+        <v>-911.4076049500883</v>
       </c>
       <c r="D98">
-        <v>188.6564515869588</v>
+        <v>186.8943950499115</v>
       </c>
       <c r="E98">
-        <v>861.0359999999998</v>
+        <v>873.0019999999997</v>
       </c>
       <c r="F98">
-        <v>1148.736</v>
+        <v>1160.702</v>
       </c>
       <c r="G98">
         <v>62.4</v>
@@ -9329,37 +9329,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M98">
-        <v>270.8719488</v>
+        <v>273.6935316</v>
       </c>
       <c r="N98">
-        <v>-177.3469488</v>
+        <v>-180.1685316</v>
       </c>
       <c r="O98">
-        <v>-26.60204232</v>
+        <v>-27.02527974</v>
       </c>
       <c r="P98">
-        <v>-150.74490648</v>
+        <v>-153.14325186</v>
       </c>
       <c r="Q98">
-        <v>-127.64490648</v>
+        <v>-130.04325186</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.817033931856563</v>
+        <v>1.074111909142084</v>
       </c>
       <c r="T98">
-        <v>14.63002269874979</v>
+        <v>19.50669693166638</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05179107715711904</v>
+        <v>0.05125714852663328</v>
       </c>
       <c r="W98">
-        <v>0.2235876640063513</v>
+        <v>0.2237135643774199</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3452738477141269</v>
+        <v>0.3417143235108885</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2492255147203598</v>
+        <v>0.2511255147203598</v>
       </c>
       <c r="C99">
-        <v>-911.4076049500883</v>
+        <v>-925.1030507575347</v>
       </c>
       <c r="D99">
-        <v>186.8943950499115</v>
+        <v>185.1649492424652</v>
       </c>
       <c r="E99">
-        <v>873.0019999999997</v>
+        <v>884.9679999999998</v>
       </c>
       <c r="F99">
-        <v>1160.702</v>
+        <v>1172.668</v>
       </c>
       <c r="G99">
         <v>62.4</v>
@@ -9411,37 +9411,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M99">
-        <v>273.6935316</v>
+        <v>276.5151144</v>
       </c>
       <c r="N99">
-        <v>-180.1685316</v>
+        <v>-182.9901144</v>
       </c>
       <c r="O99">
-        <v>-27.02527974</v>
+        <v>-27.44851716</v>
       </c>
       <c r="P99">
-        <v>-153.14325186</v>
+        <v>-155.54159724</v>
       </c>
       <c r="Q99">
-        <v>-130.04325186</v>
+        <v>-132.44159724</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.074111909142084</v>
+        <v>1.588267863713126</v>
       </c>
       <c r="T99">
-        <v>19.50669693166638</v>
+        <v>29.26004539749957</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05125714852663328</v>
+        <v>0.0507341163988105</v>
       </c>
       <c r="W99">
-        <v>0.2237135643774199</v>
+        <v>0.2238368953531605</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3417143235108885</v>
+        <v>0.3382274426587366</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2511255147203598</v>
+        <v>0.2530255147203598</v>
       </c>
       <c r="C100">
-        <v>-925.1030507575347</v>
+        <v>-938.7667828347618</v>
       </c>
       <c r="D100">
-        <v>185.1649492424652</v>
+        <v>183.467217165238</v>
       </c>
       <c r="E100">
-        <v>884.9679999999998</v>
+        <v>896.9339999999997</v>
       </c>
       <c r="F100">
-        <v>1172.668</v>
+        <v>1184.634</v>
       </c>
       <c r="G100">
         <v>62.4</v>
@@ -9493,37 +9493,37 @@
         <v>93.52499999999999</v>
       </c>
       <c r="M100">
-        <v>276.5151144</v>
+        <v>279.3366971999999</v>
       </c>
       <c r="N100">
-        <v>-182.9901144</v>
+        <v>-185.8116972</v>
       </c>
       <c r="O100">
-        <v>-27.44851716</v>
+        <v>-27.87175457999999</v>
       </c>
       <c r="P100">
-        <v>-155.54159724</v>
+        <v>-157.93994262</v>
       </c>
       <c r="Q100">
-        <v>-132.44159724</v>
+        <v>-134.83994262</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.588267863713126</v>
+        <v>3.130735727426252</v>
       </c>
       <c r="T100">
-        <v>29.26004539749957</v>
+        <v>58.52009079499914</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0507341163988105</v>
+        <v>0.05022165057660029</v>
       </c>
       <c r="W100">
-        <v>0.2238368953531605</v>
+        <v>0.2239577347940377</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3382274426587366</v>
+        <v>0.3348110038440019</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2530255147203598</v>
-      </c>
-      <c r="C101">
-        <v>-938.7667828347618</v>
-      </c>
-      <c r="D101">
-        <v>183.467217165238</v>
-      </c>
-      <c r="E101">
-        <v>896.9339999999997</v>
-      </c>
-      <c r="F101">
-        <v>1184.634</v>
-      </c>
-      <c r="G101">
-        <v>62.4</v>
-      </c>
-      <c r="H101">
-        <v>908.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>116.625</v>
-      </c>
-      <c r="K101">
-        <v>23.09999999999999</v>
-      </c>
-      <c r="L101">
-        <v>93.52499999999999</v>
-      </c>
-      <c r="M101">
-        <v>279.3366971999999</v>
-      </c>
-      <c r="N101">
-        <v>-185.8116972</v>
-      </c>
-      <c r="O101">
-        <v>-27.87175457999999</v>
-      </c>
-      <c r="P101">
-        <v>-157.93994262</v>
-      </c>
-      <c r="Q101">
-        <v>-134.83994262</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.130735727426252</v>
-      </c>
-      <c r="T101">
-        <v>58.52009079499914</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05022165057660029</v>
-      </c>
-      <c r="W101">
-        <v>0.2239577347940377</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3348110038440019</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
